--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1105,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>88.89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>77.78</v>
+        <v>77.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>77.78</v>
+        <v>77.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>55.56</v>
+        <v>55.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>66.67</v>
+        <v>66.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1428,9 +1428,10 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1442,13 +1443,14 @@
         <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
@@ -1496,10 +1498,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1556,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>66.67</v>
+        <v>66.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1613,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1670,7 +1672,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>83.33</v>
+        <v>83.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1720,14 +1722,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>70</v>
+        <v>72.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1829,14 +1831,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>72.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1933,7 +1935,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1945,7 +1947,7 @@
         <v>13</v>
       </c>
       <c r="L18" t="n">
-        <v>92.31</v>
+        <v>100</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2002,7 +2004,7 @@
         <v>13</v>
       </c>
       <c r="L19" t="n">
-        <v>92.31</v>
+        <v>92.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2056,10 +2058,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L20" t="n">
-        <v>11.11</v>
+        <v>9.5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2292,7 +2294,7 @@
         <v>19</v>
       </c>
       <c r="L24" t="n">
-        <v>26.32</v>
+        <v>26.3</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2346,10 +2348,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L25" t="n">
-        <v>33.33</v>
+        <v>28.1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2403,10 +2405,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26" t="n">
-        <v>33.33</v>
+        <v>31.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2460,10 +2462,10 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2517,10 +2519,10 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>66.67</v>
+        <v>57.1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2574,10 +2576,10 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2795,7 +2797,7 @@
         <v>15</v>
       </c>
       <c r="L33" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2887,7 +2889,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2896,10 +2898,10 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2996,7 +2998,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3008,7 +3010,7 @@
         <v>4</v>
       </c>
       <c r="L37" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3171,10 +3173,10 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L40" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3224,14 +3226,14 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>26.32</v>
+        <v>57.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3288,7 +3290,7 @@
         <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>16.67</v>
+        <v>16.7</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3397,7 +3399,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>16.67</v>
+        <v>16.7</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3593,19 +3595,19 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -3645,19 +3647,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -3695,21 +3697,26 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>YOGA</t>
         </is>
       </c>
       <c r="K50" t="n">
         <v>4</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -3747,21 +3754,26 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>YOGA</t>
         </is>
       </c>
       <c r="K51" t="n">
         <v>4</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -3806,7 +3818,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -3853,7 +3865,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3862,10 +3874,10 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -3905,7 +3917,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3917,7 +3929,7 @@
         <v>9</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -3974,7 +3986,7 @@
         <v>13</v>
       </c>
       <c r="L55" t="n">
-        <v>53.85</v>
+        <v>53.8</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -4090,10 +4102,10 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L57" t="n">
-        <v>75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -4185,7 +4197,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4197,7 +4209,7 @@
         <v>36</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -4358,7 +4370,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>91.67</v>
+        <v>91.7</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4398,19 +4410,19 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="K63" t="n">
         <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4467,7 +4479,7 @@
         <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>83.33</v>
+        <v>83.3</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -4524,7 +4536,7 @@
         <v>6</v>
       </c>
       <c r="L65" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -4547,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H722"/>
+  <dimension ref="A1:H780"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6306,13 +6318,18 @@
           <t>UNIT 1 INDUCED DRAUGHT FAN 1 IGV 10HNC01EX001</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -6329,13 +6346,18 @@
           <t>INLET ID FAN 1 PRESSURE TRANSMITTER 10HNA61CP001</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -6352,13 +6374,18 @@
           <t>INLET PRESSURE ESP PRESSURE TRANSMITTER 10HNA41CP001</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -6375,13 +6402,18 @@
           <t>OUTLET PRESSURE ESP PRESSURE TRANSMITTER 10HNA41CP002</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -6628,13 +6660,18 @@
           <t>UNIT 1 INDUCED DRAUGHT FAN 2 IGV 10HNC01EX002</t>
         </is>
       </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -6893,13 +6930,18 @@
           <t>UNIT 1 PRIMARY AIR FAN 1 IGV</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -7321,13 +7363,18 @@
           <t>UNIT 1 PRIMARY AIR FAN 2 IGV</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -7800,13 +7847,18 @@
           <t>UNIT 1 SECONDARY AIR FAN 1 IGV SA FAN 1 20HLB01EX001</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -8203,13 +8255,18 @@
           <t>UNIT 1 IGV SA FAN 2 10HLB01EX001</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -8723,13 +8780,18 @@
           <t>INSPECTION OF MFT ACTUATOR 10HHE11AA01</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -11835,18 +11897,13 @@
           <t>UNIT 1 FEED WATER INLET ECONOMIZER MOTORIZED VALVE MOTOR 30% 10LAB30AA210</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D283" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12159,13 +12216,18 @@
           <t>BEFORE DESH 2 TEMP TRANSMITTER CALIBRATION (20HAH46CT001, 10HAH36CT009, 10HAH36CT009)</t>
         </is>
       </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="D296" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -15077,13 +15139,18 @@
           <t>ACTUATOR MOV PREHEATING 1 TURBINE</t>
         </is>
       </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -15100,13 +15167,18 @@
           <t>ACTUATOR MOV PREHEATING 2 TURBINE</t>
         </is>
       </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D423" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E423" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H423" t="n">
         <v>0</v>
@@ -15307,13 +15379,18 @@
           <t>MOV TURBINE STEAM EXTRACTION-1</t>
         </is>
       </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D432" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -15330,13 +15407,18 @@
           <t>MOV TURBINE STEAM EXTRACTION-2</t>
         </is>
       </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="D433" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E433" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -15350,7 +15432,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MOV MAIN STEAM DRAIN STG-2</t>
+          <t>TURBINE CASING TEMPERATURE - INSIDE TRANSMITTER 10MAA10CT012</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -15373,7 +15455,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>TURBINE CASING TEMPERATURE - INSIDE TRANSMITTER 10MAA10CT012</t>
+          <t>TURBINE CASING TEMPERATURE - CENTER TRANSMITTER 10MAA10CT013</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -15396,7 +15478,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>TURBINE CASING TEMPERATURE - CENTER TRANSMITTER 10MAA10CT013</t>
+          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT002</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -15419,7 +15501,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT002</t>
+          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT001</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -15442,7 +15524,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS OUTLET TO EXTRACTION I - DEAERATOR I/L TEMP TRANSMITTER 10LBD11CT001</t>
+          <t>DEAERATOR PRDS TO OUTLET EXTRACTION TRANSMITTER 10LBD11CP001</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -15465,7 +15547,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS TO OUTLET EXTRACTION TRANSMITTER 10LBD11CP001</t>
+          <t>DEAERATOR PRDS TO OUTLET EXTRACTION II TRANSMITTER 10LBD11CP002</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -15488,7 +15570,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>DEAERATOR PRDS TO OUTLET EXTRACTION II TRANSMITTER 10LBD11CP002</t>
+          <t>FEEDWATER STORAGE TANK PRESSURE TRANSMITTER 10LAA20CP001</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -15511,7 +15593,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>FEEDWATER STORAGE TANK PRESSURE TRANSMITTER 10LAA20CP001</t>
+          <t>CONTROL VALVE LPH-1</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -15520,7 +15607,7 @@
         </is>
       </c>
       <c r="E441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -15534,7 +15621,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>CONTROL VALVE LPH-1</t>
+          <t>CONTROL VALVE LPH-2</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -15543,7 +15635,7 @@
         </is>
       </c>
       <c r="E442" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H442" t="n">
         <v>0</v>
@@ -15557,7 +15649,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>CONTROL VALVE LPH-2</t>
+          <t>LP HEATER 2 TRANSMITTER 10LCC40CL001</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -15580,7 +15672,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>LP HEATER 2 TRANSMITTER 10LCC40CL001</t>
+          <t>LP HEATER 2 TRANSMITTER 10LCC40CL002</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -15603,7 +15695,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>LP HEATER 2 TRANSMITTER 10LCC40CL002</t>
+          <t>LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP TRANSMITTER 10LCC20CT001</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -15626,7 +15718,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP TRANSMITTER 10LCC20CT001</t>
+          <t>FEEDWATER STORAGE TANK TRANSMITTER 10LAA20CT001</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -15649,7 +15741,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>FEEDWATER STORAGE TANK TRANSMITTER 10LAA20CT001</t>
+          <t>CYCLE MAKE UP PUMP DEAERATOR TRANSMITTER 10HGC20CF001</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -15672,7 +15764,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>CYCLE MAKE UP PUMP DEAERATOR TRANSMITTER 10HGC20CF001</t>
+          <t>DEAERATOR TANK LEVEL 1 TRANSMITTER 10LAA20CL001</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -15695,7 +15787,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 1 TRANSMITTER 10LAA20CL001</t>
+          <t>DEAERATOR TANK LEVEL 2 TRANSMITTER 10LAA20CL002</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -15718,7 +15810,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 2 TRANSMITTER 10LAA20CL002</t>
+          <t>DEAERATOR TANK LEVEL 3 TRANSMITTER 10LAA20CL003</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -15741,7 +15833,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>DEAERATOR TANK LEVEL 3 TRANSMITTER 10LAA20CL003</t>
+          <t>TURBINE EXTRACTION III TO DEAERATOR PRESSURE TRANSMITTER 10LBD20CP001</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -15764,7 +15856,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION III TO DEAERATOR PRESSURE TRANSMITTER 10LBD20CP001</t>
+          <t>TURBINE EXTRACTION III TO LPH PRESSURE TRANSMITTER 10LBD30CP001</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -15787,7 +15879,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION III TO LPH PRESSURE TRANSMITTER 10LBD30CP001</t>
+          <t>TURBINE EXTRACTION 1 TO PNEUMATIC OPERATED VALVE PRESSURE TRANSMITTER 10LBS10CP001</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -15810,7 +15902,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>TURBINE EXTRACTION 1 TO PNEUMATIC OPERATED VALVE PRESSURE TRANSMITTER 10LBS10CP001</t>
+          <t>LP HEATER 1 TRANSMITTER 10LCC30CL001</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -15833,7 +15925,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>LP HEATER 1 TRANSMITTER 10LCC30CL001</t>
+          <t>LP HEATER 1 TRANSMITTER 10LCC30CL002</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -15856,7 +15948,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>LP HEATER 1 TRANSMITTER 10LCC30CL002</t>
+          <t>FLOW CONDESATE TO LP HEATER 1 TRANSMITTER 10LCA40CF001</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -15879,7 +15971,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>FLOW CONDESATE TO LP HEATER 1 TRANSMITTER 10LCA40CF001</t>
+          <t>CONDENSATE TO LP HEATER TRANSMITTER 10LCA40CF001</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -15897,17 +15989,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0046</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>CONDENSATE TO LP HEATER TRANSMITTER 10LCA40CF001</t>
+          <t>MSW00CYE10GH101 : ALARM SYSTEM ADMIN BUILDING</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E458" t="b">
@@ -15925,7 +16017,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH101 : ALARM SYSTEM ADMIN BUILDING</t>
+          <t>MSW00CYE10GH102 : ALARM SYSTEM DG SHEET</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -15948,7 +16040,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH102 : ALARM SYSTEM DG SHEET</t>
+          <t>MSW00CYE10GH103 : PANEL MAIN FIRE ALARM SYSTEM</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -15971,7 +16063,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH103 : PANEL MAIN FIRE ALARM SYSTEM</t>
+          <t>MSW00CYE10GH104 : ALARM SYSTEM DM MCC ROOM</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -15994,7 +16086,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH104 : ALARM SYSTEM DM MCC ROOM</t>
+          <t>MSW00CYE10GH105 : ALARM SYSTEM CHP MCC</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -16017,7 +16109,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH105 : ALARM SYSTEM CHP MCC</t>
+          <t>MSW00CYE10GH106 : ALARM SYSTEM AHP MCC</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -16040,7 +16132,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH106 : ALARM SYSTEM AHP MCC</t>
+          <t>MSW00CYE10GH107 : ALARM SYSTEM COOLING WATER</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -16063,7 +16155,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH107 : ALARM SYSTEM COOLING WATER</t>
+          <t>MSW00CYE10GH108 : ALARM SYSTEM DM/RW.FW TW PUMP</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -16086,7 +16178,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH108 : ALARM SYSTEM DM/RW.FW TW PUMP</t>
+          <t>MSW00CYE10GH109 : ALARM SYSTEM WORKSHOP OFFICE ROOM</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -16109,7 +16201,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH109 : ALARM SYSTEM WORKSHOP OFFICE ROOM</t>
+          <t>MSW00CYE10GH110 : ALARM SYSTEM SWAS ROOM</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -16132,7 +16224,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH110 : ALARM SYSTEM SWAS ROOM</t>
+          <t>MSW00CYE10GH111 : ALARM SYSTEM STG BUILDING</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -16155,7 +16247,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH111 : ALARM SYSTEM STG BUILDING</t>
+          <t>MSW00CYE10GH113 : ALARM SYSTEM SWITCHYARD BUILDING</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -16178,7 +16270,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH113 : ALARM SYSTEM SWITCHYARD BUILDING</t>
+          <t>MSW00CYE10GH114 : ALARM SYSTEM REMOTE SUBSTATION BUILDING</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -16196,21 +16288,26 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>WO-100826-0046</t>
+          <t>WO-100826-0047</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>MSW00CYE10GH114 : ALARM SYSTEM REMOTE SUBSTATION BUILDING</t>
+          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E471" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -16224,7 +16321,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF001</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -16252,7 +16349,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF001</t>
+          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF002</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -16280,12 +16377,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET FLOW DP TRANSMITTER 10HLA15CF002</t>
+          <t>P.A APH OUTLET PRESSURE TRANSMITTER 10HLA15CP001</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -16303,12 +16400,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>WO-100826-0047</t>
+          <t>WO-100826-0048</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>P.A APH OUTLET PRESSURE TRANSMITTER 10HLA15CP001</t>
+          <t>AIR SUB1 FLOW DP TRANSMITTER 10HJL10CF010</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -16317,7 +16419,7 @@
         </is>
       </c>
       <c r="E475" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H475" t="n">
         <v>0</v>
@@ -16331,7 +16433,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>AIR SUB1 FLOW DP TRANSMITTER 10HJL10CF010</t>
+          <t>AIR SUB2 FLOW DP TRANSMITTER 10HJL11CF010</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -16359,7 +16461,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>AIR SUB2 FLOW DP TRANSMITTER 10HJL11CF010</t>
+          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF001</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -16387,7 +16489,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF001</t>
+          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF002</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -16415,7 +16517,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>SA APH OUTLET FLOW TRANSMITTER 10HLA25CF002</t>
+          <t>SA APH OUTLET PRESSURE TRANSMITTER 10HLA25CP001</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -16443,12 +16545,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>SA APH OUTLET PRESSURE TRANSMITTER 10HLA25CP001</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 1 20HJL10AA010</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -16457,7 +16554,7 @@
         </is>
       </c>
       <c r="E480" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -16471,7 +16568,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 1 20HJL10AA010</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 2 20HJL11AA010</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -16494,7 +16591,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SUB 2 20HJL11AA010</t>
+          <t>UNIT 1 SECONDARY AIR FAN IGV SA CONTROL DAMPER 20HLA25AA010</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -16512,17 +16609,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>WO-100826-0048</t>
+          <t>WO-100826-0049</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>UNIT 1 SECONDARY AIR FAN IGV SA CONTROL DAMPER 20HLA25AA010</t>
+          <t>PM PC OWS</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E483" t="b">
@@ -16540,7 +16637,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>PM PC OWS</t>
+          <t>PM PC EWS</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -16563,7 +16660,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>PM PC EWS</t>
+          <t>PM panel RIO</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -16581,12 +16678,17 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>WO-100826-0049</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>PM panel RIO</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM VENTING ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -16595,7 +16697,7 @@
         </is>
       </c>
       <c r="E486" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -16609,7 +16711,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM VENTING ISOLATION VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV VENTING REGULATING VALVE</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -16637,7 +16739,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV VENTING REGULATING VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM CBD ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -16665,7 +16767,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM CBD ISOLATION VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV CBD REGULATING VALVE</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -16693,7 +16795,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV CBD REGULATING VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM IBD ISOLATION VALVE</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -16721,7 +16823,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM IBD ISOLATION VALVE</t>
+          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV IBD REGULATING VALVE</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -16749,12 +16851,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>INSPECTION &amp; CALIBRATION STEAM DRUM MOV IBD REGULATING VALVE</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL001</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -16763,7 +16860,7 @@
         </is>
       </c>
       <c r="E492" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -16777,7 +16874,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL001</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL002</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -16800,7 +16897,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL002</t>
+          <t>DRUM LEVEL TRANSMITTER 10HAD10CL003</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -16823,7 +16920,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>DRUM LEVEL TRANSMITTER 10HAD10CL003</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP002</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -16846,7 +16943,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP002</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP003</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -16869,7 +16966,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP003</t>
+          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP001</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -16887,21 +16984,26 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>DRUM PRESSURE TRANSMITTER 10HAD10CP001</t>
+          <t>COMBUSTER ASH DRAIN 1 (BED ASH COOLER DRAIN) MOV 10HHC01AA001</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>M TOHER</t>
         </is>
       </c>
       <c r="E498" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -16915,7 +17017,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>COMBUSTER ASH DRAIN 1 (BED ASH COOLER DRAIN) MOV 10HHC01AA001</t>
+          <t>COMBUSTER ASH DRAIN 2 (EMERGENCY ASH DRAIN) MOV 10HHC01AA002</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -16943,7 +17045,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>COMBUSTER ASH DRAIN 2 (EMERGENCY ASH DRAIN) MOV 10HHC01AA002</t>
+          <t>LIMESTONE GATE VALVE</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -16971,7 +17073,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>LIMESTONE GATE VALVE</t>
+          <t>ACTUATOR BED MATERIAL DISCHARGE GATE VALVE 10ETG31AA01</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -16999,7 +17101,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>ACTUATOR BED MATERIAL DISCHARGE GATE VALVE 10ETG31AA01</t>
+          <t>COMBUSTOR LOWER PRESSURE TRANSMITTER 10HHC01CP001</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -17027,12 +17129,12 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>COMBUSTOR LOWER PRESSURE TRANSMITTER 10HHC01CP001</t>
+          <t>MSW20HHC10CP102 : UNIT 1 COMBUSTOR DP WITH GRATE 10HHC01CP011</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -17055,7 +17157,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>MSW20HHC10CP102 : UNIT 1 COMBUSTOR DP WITH GRATE 10HHC01CP011</t>
+          <t>MSW20HHC10CP103 : UNIT 1 COMBUSTOR UPPER DP 10HHC01CP012</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -17064,7 +17171,7 @@
         </is>
       </c>
       <c r="E504" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -17078,7 +17185,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>MSW20HHC10CP103 : UNIT 1 COMBUSTOR UPPER DP 10HHC01CP012</t>
+          <t>AIR COMBUSTOR AT LEVEL PRES TRANSMITTER 10HHC01CP060</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -17087,7 +17199,7 @@
         </is>
       </c>
       <c r="E505" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -17101,7 +17213,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>AIR COMBUSTOR AT LEVEL PRES TRANSMITTER 10HHC01CP060</t>
+          <t>MSW20HHC10CT101 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT011</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -17110,7 +17227,7 @@
         </is>
       </c>
       <c r="E506" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -17124,7 +17241,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT101 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT011</t>
+          <t>MSW20HHC10CT102 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT012</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -17147,7 +17264,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT102 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT012</t>
+          <t>MSW20HHC10CT103 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT013</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -17170,7 +17287,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT103 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT013</t>
+          <t>MSW20HHC10CT104 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT041</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -17193,7 +17310,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT104 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT041</t>
+          <t>MSW20HHC10CT105 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT042</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -17216,7 +17333,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT105 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT042</t>
+          <t>MSW20HHC10CT106 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT043</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -17239,7 +17356,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>MSW20HHC10CT106 : UNIT 1 COMBUSTOR MIDDLE TEMP 10HHC01CT043</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP003</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -17248,7 +17370,7 @@
         </is>
       </c>
       <c r="E512" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -17262,7 +17384,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP003</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP002</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -17271,7 +17398,7 @@
         </is>
       </c>
       <c r="E513" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -17285,7 +17412,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP002</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP001</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -17294,7 +17426,7 @@
         </is>
       </c>
       <c r="E514" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -17308,7 +17440,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER 10HBK01CP001</t>
+          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER 10HBK01CP030</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -17331,7 +17463,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER 10HBK01CP030</t>
+          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER 10HBK01CP050</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -17349,12 +17481,17 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0052</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER 10HBK01CP050</t>
+          <t>MSW20HDF10CP102 : UNIT 1 BACKPASS INLET PRESSURE</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -17363,7 +17500,7 @@
         </is>
       </c>
       <c r="E517" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -17377,12 +17514,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>MSW20HDF10CP102 : UNIT 1 BACKPASS INLET PRESSURE</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>CYCLONE TO SEALPOT PRESSURE TRANSMITTER 10HDF01CP001</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -17391,7 +17523,7 @@
         </is>
       </c>
       <c r="E518" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -17405,7 +17537,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>CYCLONE TO SEALPOT PRESSURE TRANSMITTER 10HDF01CP001</t>
+          <t>MSW20HDF10CT101 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -17428,7 +17560,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>MSW20HDF10CT101 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
+          <t>MSW20HDF10CT102 : UNIT 1 CYCLONE OUTLET TEMP 10HNA01CT001</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -17451,7 +17583,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MSW20HDF10CT102 : UNIT 1 CYCLONE OUTLET TEMP 10HNA01CT001</t>
+          <t>MSW20HDF10CT103 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -17474,7 +17606,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MSW20HDF10CT103 : UNIT 1 BACKPASS INLET TEMPERATURE</t>
+          <t>MSW20HDF10CT104 : UNIT 1 CYCLONE INLET TEMPERATURE</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -17492,17 +17624,17 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>WO-100826-0052</t>
+          <t>WO-100826-0053</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MSW20HDF10CT104 : UNIT 1 CYCLONE INLET TEMPERATURE</t>
+          <t>ACTUATOR DAMPER SEALPOT BLOWER 1</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>M TOHER</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E523" t="b">
@@ -17520,7 +17652,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>ACTUATOR DAMPER SEALPOT BLOWER 1</t>
+          <t>ACTUATOR DAMPER SEALPOT BLOWER 2</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -17543,7 +17675,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>ACTUATOR DAMPER SEALPOT BLOWER 2</t>
+          <t>CALIBRATION PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -17566,7 +17698,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>CALIBRATION PRESSURE TRANSMITTER</t>
+          <t>CALIBRATION TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -17584,12 +17716,17 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>WO-100826-0053</t>
+          <t>WO-100826-0054</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>CALIBRATION TEMPERATURE TRANSMITTER</t>
+          <t>ERV PRESSURE SWITCH 10LBA20CP502</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -17598,7 +17735,7 @@
         </is>
       </c>
       <c r="E527" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -17612,7 +17749,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>ERV PRESSURE SWITCH 10LBA20CP502</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT001</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -17640,12 +17777,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT001</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT002</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -17654,7 +17786,7 @@
         </is>
       </c>
       <c r="E529" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -17668,7 +17800,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT002</t>
+          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT003</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -17691,7 +17823,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT003</t>
+          <t>ACTUATOR MAIN STEAM LINE (START UP BYPASS) TO DEAERATOR PRDS I/L CV 10LBH10AA210</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -17714,7 +17846,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>ACTUATOR MAIN STEAM LINE (START UP BYPASS) TO DEAERATOR PRDS I/L CV 10LBH10AA210</t>
+          <t>MS START-UP VENT VALVE (REGULATING) MOV 10LBA21AA011</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -17737,7 +17869,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>MS START-UP VENT VALVE (REGULATING) MOV 10LBA21AA011</t>
+          <t>MS START-UP VENT VALVE (ISOLATION) MOV 10LBA21AA001</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -17760,7 +17892,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>MS START-UP VENT VALVE (ISOLATION) MOV 10LBA21AA001</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP001</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -17783,7 +17915,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP001</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP002</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -17806,7 +17938,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP002</t>
+          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP003</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -17829,7 +17961,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MAIN STEAM LIVE PRESSURE TRANSMITTER 10LAB10CP003</t>
+          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF001</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -17852,7 +17984,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF001</t>
+          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF002</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -17870,17 +18002,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>WO-100826-0054</t>
+          <t>WO-100826-0055</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION FLOW TRANSMITTER 10LBA10CF002</t>
+          <t>MSW20MAV10-M101 : UNIT 1 JACKING OIL PUMP MOTOR</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E539" t="b">
@@ -17898,7 +18030,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MSW20MAV10-M101 : UNIT 1 JACKING OIL PUMP MOTOR</t>
+          <t>MSW20MAV10CP101 : UNIT 1 JACKING OIL PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -17916,12 +18048,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>WO-100826-0055</t>
+          <t>WO-100826-0056</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MSW20MAV10CP101 : UNIT 1 JACKING OIL PRESSURE TRANSMITTER</t>
+          <t>INSPEKSI &amp; PM OIL PUMP MOTOR ( AUXILIARY, EMERGENCY, JACKING, BREATHER )</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -17944,12 +18076,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>INSPEKSI &amp; PM OIL PUMP MOTOR ( AUXILIARY, EMERGENCY, JACKING, BREATHER )</t>
+          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP001</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E542" t="b">
@@ -17967,7 +18099,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP001</t>
+          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP002</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -17990,7 +18122,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP002</t>
+          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP003</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -18008,12 +18140,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>WO-100826-0056</t>
+          <t>WO-100826-0057</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 10MAV40CP003</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP001)</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -18036,7 +18168,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP001)</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP002)</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -18059,7 +18191,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP002)</t>
+          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP003)</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -18082,7 +18214,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>VALVE POSITION BLOCK LIVE STEAM PT (20MAX45CP003)</t>
+          <t>VALVE BLOCK - OUTLET POSITION LIVE STEAM PT (20MAX45CP004)</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -18105,7 +18237,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>VALVE BLOCK - OUTLET POSITION LIVE STEAM PT (20MAX45CP004)</t>
+          <t>CONTROL OIL PRESSURE PT (20MAX40CP001)</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -18128,12 +18260,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>CONTROL OIL PRESSURE PT (20MAX40CP001)</t>
+          <t>VALVE CHEST TEMPERATURE TRANSMITTER 10MAA10CT011</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E550" t="b">
@@ -18151,12 +18283,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>VALVE CHEST TEMPERATURE TRANSMITTER 10MAA10CT011</t>
+          <t>LIVE STEAM PRESSURE TRANSMITTER 10LBA10CP001</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E551" t="b">
@@ -18174,12 +18306,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>LIVE STEAM PRESSURE TRANSMITTER 10LBA10CP001</t>
+          <t>CALIBRATION/FUNCTION TEST CONTROL VALVE</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E552" t="b">
@@ -18192,21 +18324,26 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>WO-100826-0057</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>CALIBRATION/FUNCTION TEST CONTROL VALVE</t>
+          <t>CALIBRATION/FUNCTION TEST HP BYPASS CONTROL VALVE 20LBF10AA210</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E553" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H553" t="n">
         <v>0</v>
@@ -18220,12 +18357,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>CALIBRATION/FUNCTION TEST HP BYPASS CONTROL VALVE 20LBF10AA210</t>
+          <t>HP BYPASS TEMPERATURE TRANSMITTER 10LBF10CT001</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E554" t="b">
@@ -18243,12 +18380,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>HP BYPASS TEMPERATURE TRANSMITTER 10LBF10CT001</t>
+          <t>BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E555" t="b">
@@ -18266,7 +18403,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
+          <t>MSW20LBF10CG101 : UNIT 1 STEAM BYPASS REDUCING CONTROL VALVE PRESSURE TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -18275,7 +18417,7 @@
         </is>
       </c>
       <c r="E556" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -18289,7 +18431,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>MSW20LBF10CG101 : UNIT 1 STEAM BYPASS REDUCING CONTROL VALVE PRESSURE TRANSMITTER</t>
+          <t>MSW20LBF10CP101 : UNIT 1 STEAM BYPASS REDUCING PRESSURE TRANSMITTER 10LBF10CP001</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -18312,12 +18454,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>MSW20LBF10CP101 : UNIT 1 STEAM BYPASS REDUCING PRESSURE TRANSMITTER 10LBF10CP001</t>
+          <t>MSW20LBF10CT101 : UNIT 1 STEAM BYPASS REDUCING TEMPERATURE TRANSMITTER</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E558" t="b">
@@ -18330,17 +18472,17 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>MSW20LBF10CT101 : UNIT 1 STEAM BYPASS REDUCING TEMPERATURE TRANSMITTER</t>
+          <t>DRAIN OF ESV 10MAL10AA210</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E559" t="b">
@@ -18358,7 +18500,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>DRAIN OF ESV 10MAL10AA210</t>
+          <t>DRAIN OF CV CHAMBER 10MAL20AA210</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -18381,7 +18523,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>DRAIN OF CV CHAMBER 10MAL20AA210</t>
+          <t>TURBINE DRAIN VALVE AFTER FIRST STAGE 10MAL30AA210</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -18404,7 +18546,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE AFTER FIRST STAGE 10MAL30AA210</t>
+          <t>TURBINE DRAIN VALVE 10MAL40AA210</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -18427,7 +18569,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL40AA210</t>
+          <t>TURBINE DRAIN VALVE 10MAL50AA210</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -18450,7 +18592,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL50AA210</t>
+          <t>TURBINE DRAIN VALVE 10MAL60AA210</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -18473,7 +18615,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL60AA210</t>
+          <t>TURBINE DRAIN VALVE 10MAL70AA210</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -18491,21 +18633,26 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0060</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>TURBINE DRAIN VALVE 10MAL70AA210</t>
+          <t>MSW20MAJ10-M102 : UNIT 1 VACUUM PUMP A MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E566" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H566" t="n">
         <v>0</v>
@@ -18519,16 +18666,21 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>MSW20MAJ10-M102 : UNIT 1 VACUUM PUMP A MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-1</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E567" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -18542,7 +18694,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-1</t>
+          <t>MSW20MAJ10AA101 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -18551,7 +18708,7 @@
         </is>
       </c>
       <c r="E568" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H568" t="n">
         <v>0</v>
@@ -18565,16 +18722,21 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>MSW20MAJ10AA101 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+          <t>MSW20MAJ10CG101 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E569" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -18583,21 +18745,26 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>WO-100826-0060</t>
+          <t>WO-100826-0061</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>MSW20MAJ10CG101 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+          <t>MSW20MAJ10-M202 : UNIT 1 VACUUM PUMP B MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E570" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -18611,16 +18778,21 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>MSW20MAJ10-M202 : UNIT 1 VACUUM PUMP B MOTOR (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-2</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E571" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H571" t="n">
         <v>0</v>
@@ -18634,7 +18806,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>DISCHARGE, SUCTION &amp; VENTING VALVE VACUUM PUMP-2</t>
+          <t>MSW20MAJ10AA201 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -18643,7 +18820,7 @@
         </is>
       </c>
       <c r="E572" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H572" t="n">
         <v>0</v>
@@ -18657,16 +18834,21 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>MSW20MAJ10AA201 : UNIT 1 AIR REMOVAL SYSTEM VACUUM BREAKER SOLENOID VALVE</t>
+          <t>MSW20MAJ10CG201 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>M ZAINI</t>
         </is>
       </c>
       <c r="E573" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H573" t="n">
         <v>0</v>
@@ -18675,17 +18857,17 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>WO-100826-0061</t>
+          <t>WO-100826-0062</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>MSW20MAJ10CG201 : UNIT 1 AIR REMOVAL SYSTEM POSITION TRANSMITTER</t>
+          <t>MSW20MAG10CP103 : UNIT 1 CONDENSER BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E574" t="b">
@@ -18703,7 +18885,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>MSW20MAG10CP103 : UNIT 1 CONDENSER BYPASS PRESSURE TRANSMITTER 10MAG10CP001</t>
+          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB11CT001</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -18726,7 +18908,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB11CT001</t>
+          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB12CT001</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -18749,7 +18931,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>COOLING WATER SUPPLY TEMPERATURE TRANSMITTER 10PAB12CT001</t>
+          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB21CT001</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -18772,7 +18954,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB21CT001</t>
+          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB22CT001</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -18790,12 +18972,17 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>WO-100826-0062</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>COOLING WATER RETURN TEMPERATURE TRANSMITTER 10PAB22CT001</t>
+          <t>INSPECTION FRAME MOTOR</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -18804,7 +18991,7 @@
         </is>
       </c>
       <c r="E579" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -18818,7 +19005,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>INSPECTION FRAME MOTOR</t>
+          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -18827,7 +19019,7 @@
         </is>
       </c>
       <c r="E580" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H580" t="n">
         <v>0</v>
@@ -18841,7 +19033,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+          <t>INSPECTION TAHANAN ISOLASI</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -18850,7 +19047,7 @@
         </is>
       </c>
       <c r="E581" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H581" t="n">
         <v>0</v>
@@ -18864,7 +19061,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSPECTION COOLING FAN</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -18873,7 +19075,7 @@
         </is>
       </c>
       <c r="E582" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -18887,7 +19089,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>INSPECTION COOLING FAN</t>
+          <t>INSPECTION TAHANAN WINDING</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -18910,7 +19112,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>INSPECTION TERMINASI</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -18933,7 +19135,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI</t>
+          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -18956,7 +19158,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
+          <t>CALIBRATION LIMIT SWITCH</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -18979,7 +19181,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>CALIBRATION LIMIT SWITCH</t>
+          <t>PRESSURE TRANSMITTER CONDENSATE PUMP TO DELIVERY 10LCA30CP001</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -19002,12 +19204,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>PRESSURE TRANSMITTER CONDENSATE PUMP TO DELIVERY 10LCA30CP001</t>
+          <t>ACTUATOR CONDENSATE PUMP RECIRCULATION CONTROL VALVE 10LCA31AA210</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E588" t="b">
@@ -19025,7 +19227,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>ACTUATOR CONDENSATE PUMP RECIRCULATION CONTROL VALVE 10LCA31AA210</t>
+          <t>ACTUATOR MAIN CONDENSATE CONTROL VALVE 10LCA30AA240</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -19048,7 +19250,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>ACTUATOR MAIN CONDENSATE CONTROL VALVE 10LCA30AA240</t>
+          <t>CEP DISCHARGE ISOLATION VALVE</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -19066,21 +19268,26 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0064</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>CEP DISCHARGE ISOLATION VALVE</t>
+          <t>INSPECTION FRAME MOTOR</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E591" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H591" t="n">
         <v>0</v>
@@ -19094,7 +19301,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>INSPECTION FRAME MOTOR</t>
+          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -19103,7 +19315,7 @@
         </is>
       </c>
       <c r="E592" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -19117,7 +19329,12 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
+          <t>INSPECTION TAHANAN ISOLASI</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -19126,7 +19343,7 @@
         </is>
       </c>
       <c r="E593" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -19140,7 +19357,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSPECTION COOLING FAN</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -19149,7 +19371,7 @@
         </is>
       </c>
       <c r="E594" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -19163,7 +19385,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>INSPECTION COOLING FAN</t>
+          <t>INSPECTION TAHANAN WINDING</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -19186,7 +19408,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>INSPECTION TERMINASI</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -19209,7 +19431,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>INSPECTION TERMINASI</t>
+          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -19232,7 +19454,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
+          <t>CALIBRATION LIMIT SWITCH</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -19255,12 +19477,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>CALIBRATION LIMIT SWITCH</t>
+          <t>CEP DISCHARGE ISOLATION VALVE</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E599" t="b">
@@ -19273,12 +19495,17 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>WO-100826-0064</t>
+          <t>WO-100826-0065</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>CEP DISCHARGE ISOLATION VALVE</t>
+          <t>PENGUJIAN PROTEKSI FREQUENCY</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -19287,7 +19514,7 @@
         </is>
       </c>
       <c r="E600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H600" t="n">
         <v>0</v>
@@ -19301,7 +19528,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI FREQUENCY</t>
+          <t>PENGUJIAN PROTEKSI DIFFERENSIAL GENERATOR</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -19329,7 +19556,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI DIFFERENSIAL GENERATOR</t>
+          <t>PENGUJIAN PROTEKSI SHORT CIRCUIT</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -19357,7 +19584,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI SHORT CIRCUIT</t>
+          <t>PENGUJIAN PROTEKSI OVERCURRENT</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -19385,7 +19612,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERCURRENT</t>
+          <t>PENGUJIAN PROTEKSI OVERVOLTAGE</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -19413,7 +19640,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERVOLTAGE</t>
+          <t>PENGUJIAN PROTEKSI ROTOR EARTH FAULT</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -19441,7 +19668,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI ROTOR EARTH FAULT</t>
+          <t>PENGUJIAN PROTEKSI STATOR EARTH FAULT</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -19469,12 +19696,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI STATOR EARTH FAULT</t>
-        </is>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>PENGUJIAN PROTEKSI REVERSE POWER</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -19483,7 +19705,7 @@
         </is>
       </c>
       <c r="E607" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H607" t="n">
         <v>0</v>
@@ -19497,7 +19719,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI REVERSE POWER</t>
+          <t>PENGUJIAN PROTEKSI UNDER EXCITATION</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -19520,7 +19742,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI UNDER EXCITATION</t>
+          <t>PENGUJIAN PROTEKSI OVER EXCITATION</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -19543,7 +19765,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVER EXCITATION</t>
+          <t>PENGUJIAN PROTEKSI NEGATIVE SEQUENCE</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -19566,7 +19788,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI NEGATIVE SEQUENCE</t>
+          <t>PENGUJIAN PROTEKSI OVERLOAD</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -19589,7 +19811,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERLOAD</t>
+          <t>CLEANING DAN TIGHTNING</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -19607,12 +19829,17 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>WO-100826-0065</t>
+          <t>WO-100826-0066</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>CLEANING DAN TIGHTNING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE PANEL</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -19621,7 +19848,7 @@
         </is>
       </c>
       <c r="E613" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -19635,7 +19862,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE PANEL</t>
+          <t>MEMBERSIHKAN FILTER PANEL</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -19663,7 +19890,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>MEMBERSIHKAN FILTER PANEL</t>
+          <t>PEMELIHARAAN FAN CONVERTER UNITROL</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -19691,7 +19918,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>PEMELIHARAAN FAN CONVERTER UNITROL</t>
+          <t>MEMBERSIHKAN KOMPARTEMEN DALAM PANEL</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -19719,7 +19946,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>MEMBERSIHKAN KOMPARTEMEN DALAM PANEL</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -19742,12 +19969,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>WO-100826-0066</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 1</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -19757,7 +19984,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E618" t="b">
@@ -19775,7 +20002,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 1</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 2</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -19803,7 +20030,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 2</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 3</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -19831,7 +20058,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 3</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 4</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -19859,7 +20086,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 4</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 5</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -19887,7 +20114,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 5</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 6</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -19915,7 +20142,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 6</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 7</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -19943,7 +20170,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 7</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 8</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -19971,7 +20198,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 8</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 9</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -19999,7 +20226,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 9</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 10</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -20027,7 +20254,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 10</t>
+          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 11</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -20055,7 +20282,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>CLEANING, INSPECTION, &amp; REGREASING ALL SOOT BLOWER MOTOR 11</t>
+          <t>SOOT BLOWER STEAM OUTLET TRANSMITTER 10HCB10CP001</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -20083,12 +20310,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>SOOT BLOWER STEAM OUTLET TRANSMITTER 10HCB10CP001</t>
-        </is>
-      </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>SOOT BLOWER STEAM FLOW TRANSMITTER 10HCB10CF001</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -20097,7 +20319,7 @@
         </is>
       </c>
       <c r="E630" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H630" t="n">
         <v>0</v>
@@ -20111,12 +20333,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>SOOT BLOWER STEAM FLOW TRANSMITTER 10HCB10CF001</t>
+          <t>ACTUATOR VALVE DRAIN SOOT BLOWER 10HCB10AA201</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E631" t="b">
@@ -20134,7 +20356,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>ACTUATOR VALVE DRAIN SOOT BLOWER 10HCB10AA201</t>
+          <t>SOOT BLOWER VALVE MOV 10HCB10AA001</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -20157,12 +20379,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>SOOT BLOWER VALVE MOV 10HCB10AA001</t>
+          <t>ACTUATOR SOOT BLOWER CONTROL VALVE 10HCB10EX001</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E633" t="b">
@@ -20175,17 +20397,17 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0068</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>ACTUATOR SOOT BLOWER CONTROL VALVE 10HCB10EX001</t>
+          <t>PM PC OWS</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JHON</t>
         </is>
       </c>
       <c r="E634" t="b">
@@ -20203,7 +20425,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>PM PC OWS</t>
+          <t>PM PC EWS</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -20226,7 +20448,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>PM PC EWS</t>
+          <t>PM panel RIO</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -20244,21 +20466,26 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>WO-100826-0068</t>
+          <t>WO-100826-0069</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>PM panel RIO</t>
+          <t>INSPEKSI LV TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>JHON</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E637" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H637" t="n">
         <v>0</v>
@@ -20272,7 +20499,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>INSPEKSI LV TRANSFORMER</t>
+          <t>RDC Test LV TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -20281,7 +20513,7 @@
         </is>
       </c>
       <c r="E638" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H638" t="n">
         <v>0</v>
@@ -20295,7 +20527,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>RDC Test LV TRANSFORMER</t>
+          <t>FUNGSI RACK OUT RACK IN</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -20304,7 +20541,7 @@
         </is>
       </c>
       <c r="E639" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -20318,7 +20555,12 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>FUNGSI RACK OUT RACK IN</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -20327,7 +20569,7 @@
         </is>
       </c>
       <c r="E640" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H640" t="n">
         <v>0</v>
@@ -20341,7 +20583,12 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -20350,7 +20597,7 @@
         </is>
       </c>
       <c r="E641" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -20364,7 +20611,12 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR *)sudah termasuk busbar dan busduct</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -20373,7 +20625,7 @@
         </is>
       </c>
       <c r="E642" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H642" t="n">
         <v>0</v>
@@ -20387,7 +20639,12 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR *)sudah termasuk busbar dan busduct</t>
+          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -20396,7 +20653,7 @@
         </is>
       </c>
       <c r="E643" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H643" t="n">
         <v>0</v>
@@ -20410,7 +20667,12 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -20419,7 +20681,7 @@
         </is>
       </c>
       <c r="E644" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H644" t="n">
         <v>0</v>
@@ -20433,7 +20695,12 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -20442,7 +20709,7 @@
         </is>
       </c>
       <c r="E645" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H645" t="n">
         <v>0</v>
@@ -20456,7 +20723,12 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>PERAWATAN KOMPARTEMEN TRAFO KONTROL</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -20465,7 +20737,7 @@
         </is>
       </c>
       <c r="E646" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -20479,7 +20751,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN TRAFO KONTROL</t>
+          <t>PERAWATAN KOMPARTEMEN SOOTBLOWER MCC FEEDER</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -20502,7 +20774,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN SOOTBLOWER MCC FEEDER</t>
+          <t>PERAWATAN KOMPARTEMEN TG MCC FEEDER</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -20525,7 +20797,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN TG MCC FEEDER</t>
+          <t>PERAWATAN KOMPARTEMEN ADAPTER PANEL</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -20548,7 +20820,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN ADAPTER PANEL</t>
+          <t>PENGUJIAN TAHANAN KONTAK BUSDUCT BUSTIE</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -20571,7 +20843,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSDUCT BUSTIE</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -20594,7 +20866,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -20617,7 +20889,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -20640,7 +20912,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
+          <t>PENGUJIAN ANALISA CB</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -20663,7 +20935,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
+          <t>PERAWATAN ACB ESP FEEDER</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -20686,7 +20958,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB ESP FEEDER</t>
+          <t>PENGUJIAN TAHANAN ISOLASI ACB ESP FEEDER</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -20709,7 +20981,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB ESP FEEDER</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB ESP FEEDER</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -20732,7 +21004,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB ESP FEEDER</t>
+          <t>PENGUJIAN ANALISA CB ESP FEEDER</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -20755,7 +21027,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB ESP FEEDER</t>
+          <t>PERAWATAN ACB BOILER FEEDER</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -20778,7 +21050,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB BOILER FEEDER</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB BOILER FEEDER</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -20801,7 +21073,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB BOILER FEEDER</t>
+          <t>PENGUJIAN ANALISA CB BOILER FEEDER</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -20824,7 +21096,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB BOILER FEEDER</t>
+          <t>PERAWATAN ACB COOLING TOWER MCC FEEDER</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -20847,7 +21119,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB COOLING TOWER MCC FEEDER</t>
+          <t>PENGUJIAN TAHANAN ISOLASI ACB COOLING TOWER FEEDER</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -20870,7 +21142,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB COOLING TOWER FEEDER</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB COOLING TOWER FEEDER</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -20893,7 +21165,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB COOLING TOWER FEEDER</t>
+          <t>PENGUJIAN ANALISA CB COOLING TOWER FEEDER</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -20916,7 +21188,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB COOLING TOWER FEEDER</t>
+          <t>INSPECTION HEATER BUSDUCT</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -20939,7 +21211,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>INSPECTION HEATER BUSDUCT</t>
+          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -20962,7 +21234,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
+          <t>INSPECTION SILICA BUSDUCT</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -20985,7 +21257,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>INSPECTION SILICA BUSDUCT</t>
+          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -21008,7 +21280,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
+          <t>INSPECTION CONTACT RESISTANCE BUSDUCT</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -21031,7 +21303,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>INSPECTION CONTACT RESISTANCE BUSDUCT</t>
+          <t>INSPECTION ISOLATION RESISTANCE BUSDUCT</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -21054,7 +21326,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>INSPECTION ISOLATION RESISTANCE BUSDUCT</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -21072,12 +21344,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>WO-100826-0069</t>
+          <t>WO-100826-0070</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -21100,7 +21372,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -21123,7 +21395,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -21146,7 +21418,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -21169,7 +21441,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -21192,7 +21464,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -21215,7 +21487,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>PERAWATAN MODULE WITHDRAWABLE</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -21238,7 +21510,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>PERAWATAN MODULE WITHDRAWABLE</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -21261,7 +21533,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMING</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -21284,7 +21556,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMING</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -21307,7 +21579,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB</t>
+          <t>PENGUJIAN ANALISA CB</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -21330,7 +21602,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -21348,12 +21620,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>WO-100826-0070</t>
+          <t>WO-100826-0071</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -21376,7 +21648,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -21399,7 +21671,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -21422,7 +21694,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -21445,7 +21717,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -21468,7 +21740,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -21491,7 +21763,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>PERAWATAN MODULE WITHDRAWABLE</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -21514,7 +21786,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>PERAWATAN MODULE WITHDRAWABLE</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -21532,12 +21804,17 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>WO-100826-0071</t>
+          <t>WO-100826-0072</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -21546,7 +21823,7 @@
         </is>
       </c>
       <c r="E693" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -21560,7 +21837,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>PERAWATAN BAGIAN EXTERNAL ENCLOSURE MCC</t>
+          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -21588,7 +21865,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN BUSBAR</t>
+          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -21616,7 +21893,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -21644,7 +21921,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>PERAWATAN KOMPARTEMEN KABEL</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -21672,7 +21949,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN KABEL</t>
+          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -21700,7 +21977,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>PERAWATAN KOMPARTEMEN MARSHALLING PANEL</t>
+          <t>PERAWATAN MODULE WITHDRAWABLE</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -21728,7 +22005,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>PERAWATAN MODULE WITHDRAWABLE</t>
+          <t>PERAWATAN ACB INCOMMING</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -21756,7 +22033,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>PERAWATAN ACB INCOMMING</t>
+          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -21784,7 +22061,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
+          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -21812,7 +22089,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
+          <t>PENGUJIAN ANALISA CB</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -21840,12 +22117,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
-        </is>
-      </c>
-      <c r="C704" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -21854,7 +22126,7 @@
         </is>
       </c>
       <c r="E704" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -21863,17 +22135,17 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>WO-100826-0072</t>
+          <t>WO-100826-0073</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>GLAND STEAM CONDENSER VENTING MOTOR</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="E705" t="b">
@@ -21891,7 +22163,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>GLAND STEAM CONDENSER VENTING MOTOR</t>
+          <t>GLAND STEAM PRESSURE TRANSMITTER 10MAW11CP001</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -21914,7 +22186,12 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>GLAND STEAM PRESSURE TRANSMITTER 10MAW11CP001</t>
+          <t>ACTUATOR GLAND STEAM PRESSURE CONTROL VALVE 10MAW10AA210</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -21923,7 +22200,7 @@
         </is>
       </c>
       <c r="E707" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -21937,7 +22214,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>ACTUATOR GLAND STEAM PRESSURE CONTROL VALVE 10MAW10AA210</t>
+          <t>ACTUATOR GLAND STEAM TEMPERATURE CONTROL VALVE 10LCE10AA210</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -21946,7 +22228,7 @@
         </is>
       </c>
       <c r="E708" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -21960,7 +22242,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>ACTUATOR GLAND STEAM TEMPERATURE CONTROL VALVE 10LCE10AA210</t>
+          <t>GENERAL CLEANING</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -21969,7 +22256,7 @@
         </is>
       </c>
       <c r="E709" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -21978,21 +22265,26 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>WO-100826-0073</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>GENERAL CLEANING</t>
+          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>H AIDI</t>
+          <t>FERRYUS</t>
         </is>
       </c>
       <c r="E710" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -22006,7 +22298,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>INSPECTION AND CALIBRATION OXYGEN ANALYZER</t>
+          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -22090,7 +22382,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>INLET BACKPASS PRESSURE TRANSMITTER</t>
+          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -22118,12 +22410,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER</t>
-        </is>
-      </c>
-      <c r="C715" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
+          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -22132,7 +22419,7 @@
         </is>
       </c>
       <c r="E715" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -22141,21 +22428,26 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER</t>
+          <t>Panel Bapcon - Rapcon Field 1</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E716" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -22169,7 +22461,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 1</t>
+          <t>Panel Bapcon - Rapcon Field 2</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -22197,12 +22489,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 2</t>
+          <t>Panel Bapcon - Rapcon Field 3</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -22225,7 +22517,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 3</t>
+          <t>Panel Bapcon - Rapcon Field 4</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -22248,7 +22540,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 4</t>
+          <t>Panel Bapcon - Rapcon Field 5</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -22271,7 +22563,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 5</t>
+          <t>Panel Bapcon - Rapcon Field 6</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -22289,23 +22581,1382 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 6</t>
-        </is>
-      </c>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>M IQBAL</t>
+          <t>MOV MAIN STEAM DRAIN</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="E722" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H722" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="E723" t="b">
+        <v>1</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="E724" t="b">
+        <v>0</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="E725" t="b">
+        <v>1</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>ACTUATOR OUTLET ID FAN 1 MOV 10HNA71AA001</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="E726" t="b">
+        <v>0</v>
+      </c>
+      <c r="H726" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV OUTLET PA FAN 1</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E727" t="b">
+        <v>0</v>
+      </c>
+      <c r="H727" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>WO-100826-0020</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV PA FAN 1</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E728" t="b">
+        <v>0</v>
+      </c>
+      <c r="H728" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E729" t="b">
+        <v>0</v>
+      </c>
+      <c r="H729" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>WO-100826-0026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E730" t="b">
+        <v>0</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>ACTUATOR IGV SA CONTROL DAMPER 10HLA25AA010</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E731" t="b">
+        <v>0</v>
+      </c>
+      <c r="H731" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>ACTUATOR IGV SUB 1 10HJL10AA010</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E732" t="b">
+        <v>0</v>
+      </c>
+      <c r="H732" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>ACTUATOR IGV SUB 2 10HJL11AA010</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E733" t="b">
+        <v>0</v>
+      </c>
+      <c r="H733" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>FLUIDIZING VALVE BED MATERIAL</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E734" t="b">
+        <v>0</v>
+      </c>
+      <c r="H734" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>WO-100826-0051</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E735" t="b">
+        <v>0</v>
+      </c>
+      <c r="H735" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E736" t="b">
+        <v>0</v>
+      </c>
+      <c r="H736" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E737" t="b">
+        <v>0</v>
+      </c>
+      <c r="H737" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E738" t="b">
+        <v>0</v>
+      </c>
+      <c r="H738" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E739" t="b">
+        <v>0</v>
+      </c>
+      <c r="H739" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E740" t="b">
+        <v>0</v>
+      </c>
+      <c r="H740" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>WO-100826-0050</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E741" t="b">
+        <v>0</v>
+      </c>
+      <c r="H741" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV PA FAN2</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E742" t="b">
+        <v>0</v>
+      </c>
+      <c r="H742" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>WO-100826-0024</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV OUTLET SA FAN 1</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E743" t="b">
+        <v>0</v>
+      </c>
+      <c r="H743" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>ACTUATOR HP BYPASS CONTROL VALVE 10LBF10AA210</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E744" t="b">
+        <v>0</v>
+      </c>
+      <c r="H744" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>WO-100826-0058</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 10LCE40AA210</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E745" t="b">
+        <v>0</v>
+      </c>
+      <c r="H745" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>CEP DISCHARGE VALVE</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E746" t="b">
+        <v>0</v>
+      </c>
+      <c r="H746" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>MOV MAIN STEAM DRAIN STG-2</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E747" t="b">
+        <v>0</v>
+      </c>
+      <c r="H747" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E748" t="b">
+        <v>0</v>
+      </c>
+      <c r="H748" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>WO-100826-0063</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E749" t="b">
+        <v>0</v>
+      </c>
+      <c r="H749" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV INLET ECONOMIZER</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E750" t="b">
+        <v>1</v>
+      </c>
+      <c r="H750" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>WO-100826-0037</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E751" t="b">
+        <v>1</v>
+      </c>
+      <c r="H751" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>10MAA10CP001: PRESSURE BEHIND TURBINE CONTROL</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E752" t="b">
+        <v>0</v>
+      </c>
+      <c r="H752" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>10MAX45CP004: VALVE BLOCK, OUTLET POSITION LIVE STEAM</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E753" t="b">
+        <v>0</v>
+      </c>
+      <c r="H753" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E754" t="b">
+        <v>1</v>
+      </c>
+      <c r="H754" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>WO-100826-0039</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E755" t="b">
+        <v>0</v>
+      </c>
+      <c r="H755" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E756" t="b">
+        <v>0</v>
+      </c>
+      <c r="H756" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>WO-100826-0160</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E757" t="b">
+        <v>0</v>
+      </c>
+      <c r="H757" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>10HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E758" t="b">
+        <v>0</v>
+      </c>
+      <c r="H758" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>10HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E759" t="b">
+        <v>0</v>
+      </c>
+      <c r="H759" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>10HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E760" t="b">
+        <v>0</v>
+      </c>
+      <c r="H760" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>10HLB01CP101: DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E761" t="b">
+        <v>0</v>
+      </c>
+      <c r="H761" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>10HLB02CP101: DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E762" t="b">
+        <v>0</v>
+      </c>
+      <c r="H762" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>10LAC10CP101: DP SWITCH BFP 1</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E763" t="b">
+        <v>0</v>
+      </c>
+      <c r="H763" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>WO-100826-0036</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>10LAC30CP101: DP SWITCH BFP 2</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E764" t="b">
+        <v>0</v>
+      </c>
+      <c r="H764" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="E765" t="b">
+        <v>1</v>
+      </c>
+      <c r="H765" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>MOV DISCHARGE BFP-1</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E766" t="b">
+        <v>0</v>
+      </c>
+      <c r="H766" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>WO-100826-0067</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>SOOT BLOWER CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E767" t="b">
+        <v>0</v>
+      </c>
+      <c r="H767" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ACTUATOR MOV TURBINE STOP VALVE</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>MSW</t>
+        </is>
+      </c>
+      <c r="E768" t="b">
+        <v>0</v>
+      </c>
+      <c r="H768" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>10QEB10CP001: P&amp;S BLOWER PRESS OUTLET</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E769" t="b">
+        <v>1</v>
+      </c>
+      <c r="H769" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>WO-100826-0038</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>10LAE10CF001: DESH 1 SPRAY WATER FLOW</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E770" t="b">
+        <v>0</v>
+      </c>
+      <c r="H770" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E771" t="b">
+        <v>0</v>
+      </c>
+      <c r="H771" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E772" t="b">
+        <v>0</v>
+      </c>
+      <c r="H772" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E773" t="b">
+        <v>0</v>
+      </c>
+      <c r="H773" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>10LBD10CP001: TURBINE EXTRACTION III TO DEAERATOR PRESSURE</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E774" t="b">
+        <v>0</v>
+      </c>
+      <c r="H774" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>10MAA10CP002: TURBINE EXHAUST PRESSURE</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E775" t="b">
+        <v>0</v>
+      </c>
+      <c r="H775" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E776" t="b">
+        <v>0</v>
+      </c>
+      <c r="H776" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>10LCC10CT001: LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E777" t="b">
+        <v>0</v>
+      </c>
+      <c r="H777" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>WO-100826-0045</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>10LBS10CT001: TURBINE EXTRACTION I TO LPH1 TEMP</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E778" t="b">
+        <v>0</v>
+      </c>
+      <c r="H778" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>WO-100826-0030</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>10HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E779" t="b">
+        <v>0</v>
+      </c>
+      <c r="H779" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>WO-100826-0035</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>10LBA10CP502: ERV PRESSURE SWITCH</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>JAPA</t>
+        </is>
+      </c>
+      <c r="E780" t="b">
+        <v>1</v>
+      </c>
+      <c r="H780" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22445,19 +24096,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -22643,17 +24289,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -22685,17 +24336,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -22831,17 +24487,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -22878,17 +24539,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -22925,17 +24591,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -22972,17 +24643,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -23511,17 +25187,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -23558,17 +25239,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -23746,17 +25432,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -23840,17 +25531,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -23887,17 +25583,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -24248,17 +25949,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -24295,17 +26001,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -24846,17 +26557,22 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -24987,17 +26703,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
       </c>
       <c r="J58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -25034,17 +26755,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
       </c>
       <c r="J59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -25165,17 +26891,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -25578,17 +27309,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -25620,17 +27356,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -25662,17 +27403,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -25746,17 +27492,22 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -25788,17 +27539,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
       </c>
       <c r="J76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -26651,13 +28407,13 @@
         </is>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27012,8 +28768,13 @@
           <t>0-20 bar</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -27046,8 +28807,13 @@
           <t>0-1 bar</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -27080,8 +28846,13 @@
           <t>0-1500 mbar</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -27148,8 +28919,13 @@
           <t>0-130 mmH20</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -27182,8 +28958,13 @@
           <t>0.0 - 350 mbar</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -27216,8 +28997,13 @@
           <t>0 - 100 mbar</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -27250,8 +29036,13 @@
           <t>0-350 mbar</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -27284,8 +29075,13 @@
           <t>0-350 mbar</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -27556,8 +29352,13 @@
           <t>0-130 mmH20</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -27590,8 +29391,13 @@
           <t>0 - 130 mmH20</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -27624,8 +29430,13 @@
           <t>0-250 mbar</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -27794,8 +29605,13 @@
           <t>0 -250 mbar</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -27828,8 +29644,13 @@
           <t>-10 - 60 mbar</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -27998,8 +29819,13 @@
           <t>0 - 40 bar</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -28066,8 +29892,13 @@
           <t>16 - 6716 mmH20</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -28304,8 +30135,13 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -28338,8 +30174,13 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -28372,8 +30213,13 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -29787,8 +31633,13 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -29855,8 +31706,13 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -30127,8 +31983,13 @@
           <t>0-600 °C</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -30229,8 +32090,13 @@
           <t>0-1200 °C</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>29/8/2026</t>
+        </is>
+      </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -31589,7 +33455,17 @@
         </is>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -31633,7 +33509,17 @@
         </is>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -31765,7 +33651,17 @@
         </is>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -31809,7 +33705,17 @@
         </is>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -31941,7 +33847,17 @@
         </is>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -31985,7 +33901,17 @@
         </is>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -32117,7 +34043,17 @@
         </is>
       </c>
       <c r="N28" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -32161,7 +34097,17 @@
         </is>
       </c>
       <c r="N29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -32381,7 +34327,17 @@
         </is>
       </c>
       <c r="N34" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -32581,7 +34537,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -33099,7 +35055,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M IQBAL</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="G22" t="n">

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1836,7 +1836,7 @@
         <v>11</v>
       </c>
       <c r="L16" t="n">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2097,6 +2097,7 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
@@ -2111,13 +2112,14 @@
         <v>13</v>
       </c>
       <c r="L21" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -8273,13 +8275,18 @@
           <t>MSW20HLN10-M201:UNIT 1 SECONDARY AIR FAN 2 LUBE OIL PUMP 1 MOTOR (STAND BY)</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -8296,13 +8303,18 @@
           <t>MSW20HLN10-M202:UNIT 1 SECONDARY AIR FAN 2 LUBE OIL PUMP 2 MOTOR (MAIN)</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -9134,18 +9146,13 @@
           <t>INSPECTION OF IGNITER GUN</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -9162,18 +9169,13 @@
           <t>INSPECTION OF START UP BURNER SKID DEVICE</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -9512,13 +9514,18 @@
           <t>ATOM AIR PRESSURE AFTER SUB 1 TRANSMITTER 10HJN11CP001</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -9535,13 +9542,18 @@
           <t>LDO PRESS AFTER SUB1 FVC TRANSMITTER 10HJF11CP001</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -9673,13 +9685,18 @@
           <t>ATOM AIR PRESSURE AFTER SUB 2 TRANSMITTER 10HJN12CP001</t>
         </is>
       </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -22745,13 +22762,18 @@
           <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
         </is>
       </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="D728" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E728" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -24118,7 +24140,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -25147,7 +25169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -25199,7 +25221,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -27627,19 +27649,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>SCHED-OK</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>50</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>MSW</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="J79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="b">
         <v>0</v>
@@ -28671,11 +28688,19 @@
           <t>0,7 - 14 Bar</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -28705,11 +28730,19 @@
           <t>0-14 Bar</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="H11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -28750,6 +28783,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -28856,11 +28892,19 @@
           <t>0-20 bar</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -29123,6 +29167,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -34343,7 +34390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -34395,12 +34442,12 @@
     <row r="2" ht="24.9" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. Electric Generator 31,5 MW/11 kV</t>
+          <t>BOILER TEST EQUIPMENT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -34420,7 +34467,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M ZAINI</t>
+          <t>H AIDI</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -35604,28 +35651,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Turbine</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Major Overhoul</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>MSW</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>JHON</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1029,14 +1029,9 @@
           <t>22/08/2026</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1048,7 +1043,7 @@
         <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1390,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>76.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1442,7 +1437,7 @@
         <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1499,7 +1494,7 @@
         <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>91.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1556,7 +1551,7 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1670,7 +1665,7 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1727,7 +1722,7 @@
         <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1767,7 +1762,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1779,7 +1774,7 @@
         <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2097,7 +2092,6 @@
           <t>22/08/2026</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
@@ -2119,7 +2113,6 @@
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -2351,7 +2344,7 @@
         <v>32</v>
       </c>
       <c r="L25" t="n">
-        <v>28.1</v>
+        <v>34.4</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2465,7 +2458,7 @@
         <v>12</v>
       </c>
       <c r="L27" t="n">
-        <v>33.3</v>
+        <v>58.3</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2522,7 +2515,7 @@
         <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2579,7 +2572,7 @@
         <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2728,7 +2721,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2740,7 +2733,7 @@
         <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2901,7 +2894,7 @@
         <v>56</v>
       </c>
       <c r="L35" t="n">
-        <v>10.7</v>
+        <v>17.9</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2996,6 +2989,11 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3162,9 +3160,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3176,7 +3179,7 @@
         <v>18</v>
       </c>
       <c r="L40" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3233,7 +3236,7 @@
         <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -4356,9 +4359,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4370,7 +4378,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -4422,7 +4430,7 @@
         <v>5</v>
       </c>
       <c r="L63" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -4465,9 +4473,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4479,13 +4492,14 @@
         <v>6</v>
       </c>
       <c r="L64" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -4848,18 +4862,13 @@
           <t>SOLO RUN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6032,7 +6041,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6060,7 +6069,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6312,7 +6321,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6417,18 +6426,13 @@
           <t>UNIT 1 INDUCED DRAUGHT FAN 2 INLET ACTUATOR MOV 20HNA62AA001</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -7034,18 +7038,13 @@
           <t>20HLB01CP104: LO HEADER PRESSURE LOW ALARM FOR PA FAN-1</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -7062,18 +7061,13 @@
           <t>20HLB01CP103: PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-1 START</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -7467,18 +7461,13 @@
           <t>20HLB02CP104: LO HEADER PRESSURE LOW ALARM FOR PA FAN-2</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -7495,18 +7484,13 @@
           <t>20HLB02CP103: PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-2 START</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -7523,18 +7507,13 @@
           <t>20HLB02CP102: PRESSURE SWITCH TO START LO PA FAN-2 STANDBY PUMP</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -7844,13 +7823,18 @@
           <t>MSW20HLN10-M101:UNIT 1 SECONDARY AIR FAN 1 LUBE OIL PUMP 1 MOTOR (STAND BY)</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -7867,13 +7851,18 @@
           <t>MSW20HLN10-M102:UNIT 1 SECONDARY AIR FAN 1 LUBE OIL PUMP 2 MOTOR (MAIN)</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -11853,18 +11842,13 @@
           <t>UNIT 1 FEED WATER INLET ECONOMIZER MOTORIZED VALVE ISOLATION VALVE</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D280" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -11973,13 +11957,18 @@
           <t>DISTRIBUTOR LINE TO FEEDWATER TRANSMITTER 10LAB30CP001</t>
         </is>
       </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D285" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -11996,13 +11985,18 @@
           <t>INLET FEEDWATER PRESSURE TRANSMITTER 10HAC90CP001</t>
         </is>
       </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D286" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12019,13 +12013,18 @@
           <t>INLET FEEDWATER FLOW TRANSMITTER 10HAC90CF001</t>
         </is>
       </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12042,13 +12041,18 @@
           <t>INLET FEEDWATER FLOW TRANSMITTER 10HAC90CF002</t>
         </is>
       </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D288" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -14290,13 +14294,18 @@
           <t>INSPECTION BOLT BUSBAR, FLANGE &amp; INSPECTION HOLE BUSDUCT</t>
         </is>
       </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D384" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E384" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -14336,13 +14345,18 @@
           <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
         </is>
       </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D386" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E386" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -14405,13 +14419,18 @@
           <t>CLEANING</t>
         </is>
       </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D389" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E389" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -15008,13 +15027,18 @@
           <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP001)</t>
         </is>
       </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H415" t="n">
         <v>0</v>
@@ -15031,13 +15055,18 @@
           <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP002)</t>
         </is>
       </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E416" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H416" t="n">
         <v>0</v>
@@ -15054,13 +15083,18 @@
           <t>CONDENSATE PRESSURE TO BYPASS SPRAY PRESSURE TRANSMITTER (20LCE40CP003)</t>
         </is>
       </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D417" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -16310,7 +16344,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -16338,7 +16372,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -16394,7 +16428,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -16672,7 +16706,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -16700,7 +16734,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -16728,7 +16762,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -16838,13 +16872,18 @@
           <t>DRUM LEVEL TRANSMITTER 10HAD10CL001</t>
         </is>
       </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D490" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E490" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H490" t="n">
         <v>0</v>
@@ -16861,13 +16900,18 @@
           <t>DRUM LEVEL TRANSMITTER 10HAD10CL002</t>
         </is>
       </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D491" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E491" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -16884,13 +16928,18 @@
           <t>DRUM LEVEL TRANSMITTER 10HAD10CL003</t>
         </is>
       </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D492" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E492" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H492" t="n">
         <v>0</v>
@@ -16907,13 +16956,18 @@
           <t>DRUM PRESSURE TRANSMITTER 10HAD10CP002</t>
         </is>
       </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D493" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -16930,13 +16984,18 @@
           <t>DRUM PRESSURE TRANSMITTER 10HAD10CP003</t>
         </is>
       </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E494" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H494" t="n">
         <v>0</v>
@@ -16953,13 +17012,18 @@
           <t>DRUM PRESSURE TRANSMITTER 10HAD10CP001</t>
         </is>
       </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D495" t="inlineStr">
         <is>
           <t>JHON</t>
         </is>
       </c>
       <c r="E495" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -17345,7 +17409,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -17373,7 +17437,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -17401,7 +17465,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -17427,13 +17491,18 @@
           <t>BACKPASS PRESSURE AFTER LT SH TRANSMITTER 10HBK01CP030</t>
         </is>
       </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E513" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -17450,13 +17519,18 @@
           <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER 10HBK01CP050</t>
         </is>
       </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D514" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E514" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -22104,13 +22178,18 @@
           <t>HOUSEKEEPING</t>
         </is>
       </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D702" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E702" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -22173,18 +22252,13 @@
           <t>ACTUATOR GLAND STEAM PRESSURE CONTROL VALVE 10MAW10AA210</t>
         </is>
       </c>
-      <c r="C705" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
-        </is>
-      </c>
       <c r="D705" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E705" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -22389,21 +22463,26 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>WO-100826-0074</t>
+          <t>WO-100826-0075</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>BACKPASS PRESSURE AFTER ECO TRANSMITTER</t>
+          <t>Panel Bapcon - Rapcon Field 1</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>FERRYUS</t>
+          <t>M IQBAL</t>
         </is>
       </c>
       <c r="E713" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -22417,7 +22496,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 1</t>
+          <t>Panel Bapcon - Rapcon Field 2</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -22445,12 +22524,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 2</t>
+          <t>Panel Bapcon - Rapcon Field 3</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>29/8/2026</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -22473,12 +22552,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 3</t>
-        </is>
-      </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
+          <t>Panel Bapcon - Rapcon Field 4</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -22487,7 +22561,7 @@
         </is>
       </c>
       <c r="E716" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H716" t="n">
         <v>0</v>
@@ -22501,7 +22575,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 4</t>
+          <t>Panel Bapcon - Rapcon Field 5</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -22524,7 +22598,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 5</t>
+          <t>Panel Bapcon - Rapcon Field 6</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -22542,21 +22616,21 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>WO-100826-0075</t>
+          <t>WO-100826-0059</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Panel Bapcon - Rapcon Field 6</t>
-        </is>
-      </c>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>M IQBAL</t>
+          <t>MOV MAIN STEAM DRAIN</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E719" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -22565,17 +22639,22 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>WO-100826-0059</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>MOV MAIN STEAM DRAIN</t>
+          <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E720" t="b">
@@ -22588,17 +22667,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0039</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
-        </is>
-      </c>
-      <c r="C721" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
+          <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -22607,7 +22681,7 @@
         </is>
       </c>
       <c r="E721" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -22616,12 +22690,17 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>WO-100826-0039</t>
+          <t>WO-100826-0160</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
+          <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -22630,7 +22709,7 @@
         </is>
       </c>
       <c r="E722" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -22644,7 +22723,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
+          <t>ACTUATOR OUTLET ID FAN 1 MOV 10HNA71AA001</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -22662,21 +22741,26 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0020</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>ACTUATOR OUTLET ID FAN 1 MOV 10HNA71AA001</t>
+          <t>ACTUATOR MOV OUTLET PA FAN 1</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E724" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H724" t="n">
         <v>0</v>
@@ -22690,7 +22774,12 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV OUTLET PA FAN 1</t>
+          <t>ACTUATOR MOV PA FAN 1</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -22699,7 +22788,7 @@
         </is>
       </c>
       <c r="E725" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H725" t="n">
         <v>0</v>
@@ -22708,12 +22797,17 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>WO-100826-0020</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PA FAN 1</t>
+          <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -22722,7 +22816,7 @@
         </is>
       </c>
       <c r="E726" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -22731,12 +22825,17 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0026</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
+          <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -22745,7 +22844,7 @@
         </is>
       </c>
       <c r="E727" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H727" t="n">
         <v>0</v>
@@ -22754,17 +22853,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>WO-100826-0026</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>ACTUATOR IGV SA FAN 2 10HLB02EX001</t>
-        </is>
-      </c>
-      <c r="C728" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
+          <t>ACTUATOR IGV SA CONTROL DAMPER 10HLA25AA010</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -22773,7 +22867,7 @@
         </is>
       </c>
       <c r="E728" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -22787,7 +22881,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>ACTUATOR IGV SA CONTROL DAMPER 10HLA25AA010</t>
+          <t>ACTUATOR IGV SUB 1 10HJL10AA010</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -22810,7 +22904,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>ACTUATOR IGV SUB 1 10HJL10AA010</t>
+          <t>ACTUATOR IGV SUB 2 10HJL11AA010</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -22828,12 +22922,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0051</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>ACTUATOR IGV SUB 2 10HJL11AA010</t>
+          <t>FLUIDIZING VALVE BED MATERIAL</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -22856,7 +22950,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>FLUIDIZING VALVE BED MATERIAL</t>
+          <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -22874,12 +22968,17 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>WO-100826-0051</t>
+          <t>WO-100826-0050</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
+          <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -22888,7 +22987,7 @@
         </is>
       </c>
       <c r="E733" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -22902,7 +23001,12 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
+          <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -22911,7 +23015,7 @@
         </is>
       </c>
       <c r="E734" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H734" t="n">
         <v>0</v>
@@ -22925,7 +23029,12 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
+          <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -22934,7 +23043,7 @@
         </is>
       </c>
       <c r="E735" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -22948,7 +23057,12 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
+          <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -22957,7 +23071,7 @@
         </is>
       </c>
       <c r="E736" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -22971,7 +23085,12 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
+          <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -22980,7 +23099,7 @@
         </is>
       </c>
       <c r="E737" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H737" t="n">
         <v>0</v>
@@ -22994,7 +23113,12 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
+          <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -23003,7 +23127,7 @@
         </is>
       </c>
       <c r="E738" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H738" t="n">
         <v>0</v>
@@ -23012,12 +23136,17 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>WO-100826-0050</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
+          <t>ACTUATOR MOV PA FAN2</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -23026,7 +23155,7 @@
         </is>
       </c>
       <c r="E739" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -23035,12 +23164,17 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0024</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV PA FAN2</t>
+          <t>ACTUATOR MOV OUTLET SA FAN 1</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -23049,7 +23183,7 @@
         </is>
       </c>
       <c r="E740" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H740" t="n">
         <v>0</v>
@@ -23058,12 +23192,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>WO-100826-0024</t>
+          <t>WO-100826-0058</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV OUTLET SA FAN 1</t>
+          <t>ACTUATOR HP BYPASS CONTROL VALVE 10LBF10AA210</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -23086,7 +23220,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>ACTUATOR HP BYPASS CONTROL VALVE 10LBF10AA210</t>
+          <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 10LCE40AA210</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -23104,12 +23238,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>WO-100826-0058</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 10LCE40AA210</t>
+          <t>CEP DISCHARGE VALVE</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -23132,7 +23266,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>CEP DISCHARGE VALVE</t>
+          <t>MOV MAIN STEAM DRAIN STG-2</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -23141,7 +23280,7 @@
         </is>
       </c>
       <c r="E744" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -23155,7 +23294,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>MOV MAIN STEAM DRAIN STG-2</t>
+          <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -23173,12 +23312,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0063</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
+          <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -23196,12 +23335,17 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>WO-100826-0063</t>
+          <t>WO-100826-0037</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
+          <t>ACTUATOR MOV INLET ECONOMIZER</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -23210,7 +23354,7 @@
         </is>
       </c>
       <c r="E747" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H747" t="n">
         <v>0</v>
@@ -23224,7 +23368,12 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV INLET ECONOMIZER</t>
+          <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -23242,21 +23391,21 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>WO-100826-0037</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
+          <t>10MAA10CP001: PRESSURE BEHIND TURBINE CONTROL</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E749" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -23270,7 +23419,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>10MAA10CP001: PRESSURE BEHIND TURBINE CONTROL</t>
+          <t>10MAX45CP004: VALVE BLOCK, OUTLET POSITION LIVE STEAM</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -23288,12 +23437,17 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0039</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>10MAX45CP004: VALVE BLOCK, OUTLET POSITION LIVE STEAM</t>
+          <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -23302,7 +23456,7 @@
         </is>
       </c>
       <c r="E751" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -23316,7 +23470,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
+          <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -23334,12 +23493,17 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>WO-100826-0039</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
+          <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -23348,7 +23512,7 @@
         </is>
       </c>
       <c r="E753" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -23357,12 +23521,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0160</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
+          <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -23380,12 +23544,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>WO-100826-0160</t>
+          <t>WO-100826-0030</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
+          <t>10HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -23408,7 +23572,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>10HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
+          <t>10HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -23426,12 +23590,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>WO-100826-0030</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>10HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
+          <t>10HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -23454,7 +23618,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>10HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
+          <t>10HLB01CP101: DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -23477,7 +23641,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>10HLB01CP101: DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
+          <t>10HLB02CP101: DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -23500,7 +23664,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>10HLB02CP101: DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
+          <t>10LAC10CP101: DP SWITCH BFP 1</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
@@ -23518,12 +23682,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0036</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>10LAC10CP101: DP SWITCH BFP 1</t>
+          <t>10LAC30CP101: DP SWITCH BFP 2</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
@@ -23541,21 +23705,26 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>WO-100826-0036</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>10LAC30CP101: DP SWITCH BFP 2</t>
+          <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>JAPA</t>
+          <t>AMP</t>
         </is>
       </c>
       <c r="E762" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -23564,26 +23733,21 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
-        </is>
-      </c>
-      <c r="C763" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
+          <t>MOV DISCHARGE BFP-1</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>AMP</t>
+          <t>MSW</t>
         </is>
       </c>
       <c r="E763" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H763" t="n">
         <v>0</v>
@@ -23592,12 +23756,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0067</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>MOV DISCHARGE BFP-1</t>
+          <t>SOOT BLOWER CONTROL VALVE</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -23615,12 +23779,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>WO-100826-0067</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>SOOT BLOWER CONTROL VALVE</t>
+          <t>ACTUATOR MOV TURBINE STOP VALVE</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -23638,21 +23802,26 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>ACTUATOR MOV TURBINE STOP VALVE</t>
+          <t>10QEB10CP001: P&amp;S BLOWER PRESS OUTLET</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>MSW</t>
+          <t>JAPA</t>
         </is>
       </c>
       <c r="E766" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -23661,12 +23830,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0038</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>10QEB10CP001: P&amp;S BLOWER PRESS OUTLET</t>
+          <t>10LAE10CF001: DESH 1 SPRAY WATER FLOW</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -23689,12 +23858,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>WO-100826-0038</t>
+          <t>WO-100826-0045</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>10LAE10CF001: DESH 1 SPRAY WATER FLOW</t>
+          <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
@@ -23717,7 +23886,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
+          <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -23740,7 +23909,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
+          <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -23763,7 +23932,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
+          <t>10LBD10CP001: TURBINE EXTRACTION III TO DEAERATOR PRESSURE</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
@@ -23786,7 +23955,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>10LBD10CP001: TURBINE EXTRACTION III TO DEAERATOR PRESSURE</t>
+          <t>10MAA10CP002: TURBINE EXHAUST PRESSURE</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -23809,7 +23978,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>10MAA10CP002: TURBINE EXHAUST PRESSURE</t>
+          <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
@@ -23832,7 +24001,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
+          <t>10LCC10CT001: LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
@@ -23855,7 +24024,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>10LCC10CT001: LPH II - TUBE SIDE OUTLET TO DEAERATOR TEMP</t>
+          <t>10LBS10CT001: TURBINE EXTRACTION I TO LPH1 TEMP</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
@@ -23873,12 +24042,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>WO-100826-0045</t>
+          <t>WO-100826-0030</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>10LBS10CT001: TURBINE EXTRACTION I TO LPH1 TEMP</t>
+          <t>10HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
@@ -23896,12 +24065,17 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>WO-100826-0030</t>
+          <t>WO-100826-0035</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>10HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
+          <t>10LBA10CP502: ERV PRESSURE SWITCH</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -23910,7 +24084,7 @@
         </is>
       </c>
       <c r="E777" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -23919,17 +24093,17 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>WO-100826-0035</t>
+          <t>WO-100826-0074</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>10LBA10CP502: ERV PRESSURE SWITCH</t>
+          <t>10HBK01CP050: BACKPASS PRESSURE AFTER ECO</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
@@ -24087,10 +24261,10 @@
         <v>50</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -24132,22 +24306,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>29/08/2026</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -24575,17 +24744,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -24622,14 +24796,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
@@ -24669,17 +24843,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -24716,14 +24895,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -25030,17 +25209,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -25072,17 +25256,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -25114,17 +25303,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -26106,17 +26300,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -26148,17 +26347,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -26190,17 +26394,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -26232,17 +26441,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -26274,17 +26488,22 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -26316,17 +26535,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -26358,17 +26582,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -26912,17 +27141,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -26959,14 +27193,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -27006,14 +27240,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -27053,14 +27287,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SCHED-OK</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -28206,6 +28440,11 @@
       <c r="H92" t="n">
         <v>100</v>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
@@ -28247,6 +28486,11 @@
       </c>
       <c r="H93" t="n">
         <v>100</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J93" t="b">
         <v>1</v>
@@ -28412,14 +28656,19 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -29268,11 +29517,19 @@
           <t>0-5000 mmH20</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -29302,11 +29559,19 @@
           <t>0-5000 mmH20</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -29336,11 +29601,19 @@
           <t>0-180 bar</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -29555,11 +29828,19 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -29589,11 +29870,19 @@
           <t>0.00 - 160.00 bar</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -29701,11 +29990,19 @@
           <t>-70 - 70 mbar</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -29735,11 +30032,19 @@
           <t>-910 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -29769,11 +30074,19 @@
           <t>-910 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -29803,11 +30116,19 @@
           <t>-910 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -29949,11 +30270,19 @@
           <t>0 - 160 Bar</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
+      </c>
+      <c r="M44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -29983,11 +30312,19 @@
           <t>0 - 160 Bar</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
+      </c>
+      <c r="M45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -30017,11 +30354,19 @@
           <t>0 - 160 Bar</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -30155,7 +30500,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -30163,6 +30508,9 @@
       </c>
       <c r="L50" t="n">
         <v>0</v>
+      </c>
+      <c r="M50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -30194,7 +30542,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="H51" t="b">
@@ -30202,6 +30550,9 @@
       </c>
       <c r="L51" t="n">
         <v>0</v>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -30233,7 +30584,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>29/8/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -30241,6 +30592,9 @@
       </c>
       <c r="L52" t="n">
         <v>0</v>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -30780,11 +31134,19 @@
           <t>0 -25 Bar</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -30814,11 +31176,19 @@
           <t>0 -25 Bar</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -30848,11 +31218,19 @@
           <t>0 -25 Bar</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -33490,17 +33868,7 @@
         </is>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -33544,17 +33912,7 @@
         </is>
       </c>
       <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -33686,17 +34044,7 @@
         </is>
       </c>
       <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -33740,17 +34088,7 @@
         </is>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -33882,17 +34220,7 @@
         </is>
       </c>
       <c r="N24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -33936,17 +34264,7 @@
         </is>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -34078,17 +34396,7 @@
         </is>
       </c>
       <c r="N28" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -34132,17 +34440,7 @@
         </is>
       </c>
       <c r="N29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1385,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>82.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>11</v>
       </c>
       <c r="L14" t="n">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>32</v>
       </c>
       <c r="L25" t="n">
-        <v>34.4</v>
+        <v>31.2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>15</v>
       </c>
       <c r="L33" t="n">
-        <v>6.7</v>
+        <v>93.3</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>56</v>
       </c>
       <c r="L35" t="n">
-        <v>17.9</v>
+        <v>35.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -4499,7 +4499,6 @@
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
@@ -7772,13 +7771,18 @@
           <t>SA FAN 1 OUTLET PRESSURE TRANSMITTER 10HLB01CP001</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -14475,13 +14479,18 @@
           <t>MSW20BBA10GS102:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 1 PA FAN 1</t>
         </is>
       </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -14498,13 +14507,18 @@
           <t>MSW20BBA10GS103:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 2 PA FAN 2</t>
         </is>
       </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D392" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E392" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -14521,13 +14535,18 @@
           <t>MSW20BBA10GS104:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 3 SA FAN 1</t>
         </is>
       </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D393" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -14544,13 +14563,18 @@
           <t>MSW20BBA10GS105:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 4 SA FAN 2</t>
         </is>
       </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D394" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -14567,13 +14591,18 @@
           <t>MSW20BBA10GS106:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 5 ID FAN 1</t>
         </is>
       </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D395" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -14590,13 +14619,18 @@
           <t>MSW20BBA10GS107:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 6 ID FAN 2</t>
         </is>
       </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D396" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -14613,13 +14647,18 @@
           <t>MSW20BBA10GS108:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 8 BF PUMP 1</t>
         </is>
       </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D397" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -14636,13 +14675,18 @@
           <t>MSW20BBA10GS109:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 9 BF PUMP 2</t>
         </is>
       </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -14659,13 +14703,18 @@
           <t>MSW20BBA10GS110:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 7 CW PUMP 3</t>
         </is>
       </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -14682,13 +14731,18 @@
           <t>MSW20BBA10GS111:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 11 CW PUMP 4</t>
         </is>
       </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E400" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -14705,13 +14759,18 @@
           <t>MSW20BBA10GS112:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 OUTGOING FEEDER 12 CW PUMP 5</t>
         </is>
       </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D401" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E401" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -14728,13 +14787,18 @@
           <t>MSW20BBA10GS113:UNIT 1 SWITCHGEAR 6,6KV UNIT 1 TRAFO FEEDER</t>
         </is>
       </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E402" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -14751,13 +14815,18 @@
           <t>UNIT 1 SWITCHGEAR 6,6KV UNIT 1 ADAPTER</t>
         </is>
       </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E403" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -15545,13 +15614,18 @@
           <t>DEAERATOR PRDS TO OUTLET EXTRACTION TRANSMITTER 10LBD11CP001</t>
         </is>
       </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D436" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E436" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H436" t="n">
         <v>0</v>
@@ -15568,13 +15642,18 @@
           <t>DEAERATOR PRDS TO OUTLET EXTRACTION II TRANSMITTER 10LBD11CP002</t>
         </is>
       </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D437" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -15591,13 +15670,18 @@
           <t>FEEDWATER STORAGE TANK PRESSURE TRANSMITTER 10LAA20CP001</t>
         </is>
       </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D438" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E438" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -15762,13 +15846,18 @@
           <t>CYCLE MAKE UP PUMP DEAERATOR TRANSMITTER 10HGC20CF001</t>
         </is>
       </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D445" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E445" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -15785,13 +15874,18 @@
           <t>DEAERATOR TANK LEVEL 1 TRANSMITTER 10LAA20CL001</t>
         </is>
       </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D446" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E446" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -15831,13 +15925,18 @@
           <t>DEAERATOR TANK LEVEL 3 TRANSMITTER 10LAA20CL003</t>
         </is>
       </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D448" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E448" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -17782,18 +17881,13 @@
           <t>ERV PRESSURE SWITCH 10LBA20CP502</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D525" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E525" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -22698,18 +22792,13 @@
           <t>ACTUATOR INLET ID FAN 1 MOV 10HNA61AA001</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
       <c r="D722" t="inlineStr">
         <is>
           <t>AMP</t>
         </is>
       </c>
       <c r="E722" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H722" t="n">
         <v>0</v>
@@ -23866,13 +23955,18 @@
           <t>10LAA10CP001: FEEDWATER STORAGE TANK PRESSURE</t>
         </is>
       </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D768" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E768" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H768" t="n">
         <v>0</v>
@@ -23889,13 +23983,18 @@
           <t>10HGC10CF001: CYCLE MAKE UP PUMP DEAERATOR</t>
         </is>
       </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D769" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E769" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H769" t="n">
         <v>0</v>
@@ -23912,13 +24011,18 @@
           <t>10LAA10CL001: DEAERATOR TANK LEVEL 1</t>
         </is>
       </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D770" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E770" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -23981,13 +24085,18 @@
           <t>10LAA10CT001: FEEDWATER STORAGE TANK</t>
         </is>
       </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D773" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E773" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H773" t="n">
         <v>0</v>
@@ -24073,18 +24182,13 @@
           <t>10LBA10CP502: ERV PRESSURE SWITCH</t>
         </is>
       </c>
-      <c r="C777" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D777" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E777" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H777" t="n">
         <v>0</v>
@@ -30624,11 +30728,19 @@
           <t>0 - 10 Bar</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -30658,11 +30770,19 @@
           <t>0 - 10 Bar</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -30692,11 +30812,19 @@
           <t>0 - 10 Bar</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -30794,11 +30922,19 @@
           <t>0 - 100 Kpa</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -30828,11 +30964,19 @@
           <t>-1750 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -30868,6 +31012,9 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -30896,11 +31043,19 @@
           <t>-1750 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="H61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -33105,7 +33260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33258,7 +33413,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8 Bar</t>
+          <t>8 Bar (HIGH)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -33266,16 +33421,44 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -33284,12 +33467,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ATOM AIR INKET PRESSURE LOW</t>
+          <t>LDO PRESSURE LOW TRIP FOR SUB 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10HJN11CP301</t>
+          <t>10HJF11CP302</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -33302,24 +33485,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>5.0 Kg/Cm2</t>
+          <t>2.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -33328,12 +33514,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LDO PRESSURE LOW TRIP FOR SUB 1</t>
+          <t>ATOM AIR PRESSURE LOW TRIP FOR SUB 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10HJF11CP302</t>
+          <t>10HJN11CP302</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -33358,12 +33544,15 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -33372,12 +33561,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ATOM AIR PRESSURE LOW TRIP FOR SUB 1</t>
+          <t>LDO PRESSURE HIGH TRIP FOR SUB 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10HJN11CP302</t>
+          <t>10HJF11CP303</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -33390,24 +33579,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.5 Kg/Cm2</t>
+          <t>13.0 Kg/Cm2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -33416,12 +33608,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LDO PRESSURE HIGH TRIP FOR SUB 1</t>
+          <t>LDO PRESSURE LOW TRIP FOR SUB 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10HJF11CP303</t>
+          <t>10HJF12CP302</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -33429,29 +33621,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SUB 1</t>
+          <t>SUB 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13.0 Kg/Cm2</t>
+          <t>2.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -33460,12 +33655,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LDO PRESSURE LOW TRIP FOR SUB 2</t>
+          <t>ATOM AIR PRESSURE LOW TRIP FOR SUB 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10HJF12CP302</t>
+          <t>10HJN12CP302</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -33490,12 +33685,15 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -33504,12 +33702,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ATOM AIR PRESSURE LOW TRIP FOR SUB 2</t>
+          <t>LDO PRESSURE HIGH TRIP FOR SUB 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10HJN12CP302</t>
+          <t>10HJF12CP303</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -33522,24 +33720,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.5 Kg/Cm2</t>
+          <t>13.0 Kg/Cm2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -33548,12 +33749,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LDO PRESSURE HIGH TRIP FOR SUB 2</t>
+          <t>LDO PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10HJF12CP303</t>
+          <t>10HJF13CP302</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -33561,29 +33762,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SUB 2</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.0 Kg/Cm2</t>
+          <t>2.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -33592,12 +33796,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LDO PRESSURE LOW TRIP FOR LANCES</t>
+          <t>ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10HJF13CP302</t>
+          <t>10HJN13CP302</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -33605,7 +33809,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -33613,16 +33817,24 @@
           <t>2.5 Kg/Cm2</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -33631,12 +33843,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
+          <t>LDO PRESSURE HIGH TRIP FOR LANCES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10HJN13CP302</t>
+          <t>10HJF13CP303</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -33644,24 +33856,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.5 Kg/Cm2</t>
+          <t>13.0 Kg/Cm2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -33670,12 +33890,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LDO PRESSURE HIGH TRIP FOR LANCES</t>
+          <t>LPG GAS PRESSURE BEFORE MTV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10HJF13CP303</t>
+          <t>10HJG89CP301</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -33683,24 +33903,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>SUB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13.0 Kg/Cm2</t>
+          <t>1.5 Kg/Cm2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N12" t="b">
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -33709,12 +33937,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LPG GAS PRESSURE BEFORE MTV</t>
+          <t>SCANNER AIR PRESSURE OK 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10HJG89CP301</t>
+          <t>10HJG69CP301</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -33727,7 +33955,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.5 Kg/Cm2</t>
+          <t>0.6 Kg/Cm2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -33739,12 +33967,15 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -33753,12 +33984,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SCANNER AIR PRESSURE OK 1</t>
+          <t>SCANNER AIR PRESSURE OK 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10HJG69CP301</t>
+          <t>10HJG69CP302</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -33771,7 +34002,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.6 Kg/Cm2</t>
+          <t>2.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -33783,12 +34014,15 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -33797,12 +34031,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SCANNER AIR PRESSURE OK 2</t>
+          <t>LO HEADER PRESSURE LOW ALARM FOR PA FAN-1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10HJG69CP302</t>
+          <t>10HLB01CP104</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -33810,29 +34044,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SUB</t>
+          <t>PA Fan 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.5 Kg/Cm2</t>
+          <t>0.4 Kg/Cm2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N15" t="b">
         <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -33841,12 +34078,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LO HEADER PRESSURE LOW ALARM FOR PA FAN-1</t>
+          <t>PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-1 START</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>10HLB01CP104</t>
+          <t>10HLB01CP103</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -33859,24 +34096,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.4 Kg/Cm2</t>
+          <t>0.8 Kg/Cm2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N16" t="b">
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -33885,12 +34125,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-1 START</t>
+          <t>PRESSURE SWITCH TO START LO PA FAN-1 STANDBY PUMP</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10HLB01CP103</t>
+          <t>10HLB01CP102</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -33903,24 +34143,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.8 Kg/Cm2</t>
+          <t>0.6 Kg/Cm2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N17" t="b">
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -33929,12 +34172,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START LO PA FAN-1 STANDBY PUMP</t>
+          <t>DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10HLB01CP102</t>
+          <t>10HLB01CP101</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -33947,24 +34190,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.6 Kg/Cm2</t>
+          <t>0.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N18" t="b">
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -33973,12 +34219,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DP SWITCH ACRROS LO TANK FOR PA FAN-1</t>
+          <t>LO HEADER PRESSURE LOW ALARM FOR PA FAN-2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10HLB01CP101</t>
+          <t>10HLB02CP104</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -33986,29 +34232,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PA Fan 1</t>
+          <t>PA Fan 2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.5 Kg/Cm2</t>
+          <t>0.4 Kg/Cm2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -34017,12 +34266,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LO HEADER PRESSURE LOW ALARM FOR PA FAN-2</t>
+          <t>PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-2 START</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10HLB02CP104</t>
+          <t>10HLB02CP103</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -34035,24 +34284,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.4 Kg/Cm2</t>
+          <t>0.8 Kg/Cm2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -34061,12 +34313,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START PERMISSIVE FOR PA FAN-2 START</t>
+          <t>PRESSURE SWITCH TO START LO PA FAN-2 STANDBY PUMP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10HLB02CP103</t>
+          <t>10HLB02CP102</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -34079,24 +34331,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.8 Kg/Cm2</t>
+          <t>0.6 Kg/Cm2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -34105,12 +34360,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START LO PA FAN-2 STANDBY PUMP</t>
+          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10HLB02CP102</t>
+          <t>10HLB02CP101</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -34123,24 +34378,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.6 Kg/Cm2</t>
+          <t>0.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N22" t="b">
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -34149,12 +34407,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
+          <t>LO HEADER PRESSURE LOW ALARM FOR SA FAN-1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10HLB02CP101</t>
+          <t>10HLB05CP104</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -34162,29 +34420,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PA Fan 2</t>
+          <t>SA Fan 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.5 Kg/Cm2</t>
+          <t>0.4 Kg/Cm2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N23" t="b">
         <v>0</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -34193,12 +34454,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LO HEADER PRESSURE LOW ALARM FOR SA FAN-1</t>
+          <t>PRESSURE SWITCH TO START PERMISSIVE FOR SA FAN-1 START</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10HLB05CP104</t>
+          <t>10HLB05CP103</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -34211,24 +34472,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.4 Kg/Cm2</t>
+          <t>0.8 Kg/Cm2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -34237,12 +34501,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START PERMISSIVE FOR SA FAN-1 START</t>
+          <t>PRESSURE SWITCH TO START LO SA FAN-1 STANDBY PUMP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10HLB05CP103</t>
+          <t>10HLB05CP102</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -34255,24 +34519,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.8 Kg/Cm2</t>
+          <t>0.6 Kg/Cm2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N25" t="b">
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -34281,12 +34548,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START LO SA FAN-1 STANDBY PUMP</t>
+          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10HLB05CP102</t>
+          <t>10HLB05CP101</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -34299,24 +34566,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.6 Kg/Cm2</t>
+          <t>0.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N26" t="b">
         <v>0</v>
       </c>
       <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -34325,12 +34595,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-1</t>
+          <t>LO HEADER PRESSURE LOW ALARM FOR SA FAN-2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10HLB05CP101</t>
+          <t>10HLB06CP104</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -34338,29 +34608,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SA Fan 1</t>
+          <t>SA Fan 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.5 Kg/Cm2</t>
+          <t>0.4 Kg/Cm2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N27" t="b">
         <v>0</v>
       </c>
       <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -34369,12 +34642,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LO HEADER PRESSURE LOW ALARM FOR SA FAN-2</t>
+          <t>PRESSURE SWITCH TO START PERMISSIVE FOR SA FAN-2 START</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10HLB06CP104</t>
+          <t>10HLB06CP103</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -34387,24 +34660,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.4 Kg/Cm2</t>
+          <t>0.8 Kg/Cm2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N28" t="b">
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -34413,12 +34689,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START PERMISSIVE FOR SA FAN-2 START</t>
+          <t>PRESSURE SWITCH TO START LO SA  FAN-2 STANDBY PUMP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10HLB06CP103</t>
+          <t>10HLB06CP102</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -34431,24 +34707,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.8 Kg/Cm2</t>
+          <t>0.6 Kg/Cm2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="N29" t="b">
         <v>0</v>
       </c>
       <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -34457,12 +34736,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PRESSURE SWITCH TO START LO SA  FAN-2 STANDBY PUMP</t>
+          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10HLB06CP102</t>
+          <t>10HLB06CP101</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -34475,38 +34754,41 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.6 Kg/Cm2</t>
+          <t>0.5 Kg/Cm2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N30" t="b">
         <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BOILER</t>
+          <t>STG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DP SWITCH ACRROS LO TANK FOR SA FAN-2</t>
+          <t>DP SWITCH BFP 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10HLB06CP101</t>
+          <t>10LAC10CP101</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -34514,12 +34796,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SA Fan 2</t>
+          <t>BFP 1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.5 Kg/Cm2</t>
+          <t>0.5 Bar</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -34531,12 +34813,15 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -34545,12 +34830,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DP SWITCH BFP 1</t>
+          <t>DP SWITCH BFP 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10LAC10CP101</t>
+          <t>10LAC30CP101</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -34558,7 +34843,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BFP 1</t>
+          <t>BFP 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -34575,26 +34860,29 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STG</t>
+          <t>BOILER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DP SWITCH BFP 2</t>
+          <t>ERV PRESSURE SWITCH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10LAC30CP101</t>
+          <t>10LBA10CP502</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -34602,12 +34890,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BFP 2</t>
+          <t>ERV</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.5 Bar</t>
+          <t>93 Bar (HIGH)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -34615,16 +34903,24 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="N33" t="b">
         <v>0</v>
       </c>
       <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -34633,12 +34929,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ERV PRESSURE SWITCH</t>
+          <t>ATOM AIR INLET PRESSURE LOW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10LBA10CP502</t>
+          <t>10HJN11CP301</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -34646,12 +34942,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ERV</t>
+          <t>SUB 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>93 Bar</t>
+          <t>5.0 Kg/Cm2 (LOW)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -34659,20 +34955,18 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="N34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -399,14 +399,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="B2:G28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.35" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -421,7 +420,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -486,8 +484,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -552,8 +548,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -600,9 +594,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -700,13 +691,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="B2:B30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="16.35" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -714,7 +704,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
         <is>
@@ -722,7 +711,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" s="8" t="n"/>
     </row>
@@ -1041,9 +1029,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1055,7 +1048,7 @@
         <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1098,9 +1091,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1112,7 +1110,7 @@
         <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1390,7 +1388,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FINISH</t>
+          <t>IN PROGRESS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1402,7 +1400,7 @@
         <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2532,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>85.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2589,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>71.40000000000001</v>
+        <v>28.6</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2911,7 +2909,7 @@
         <v>56</v>
       </c>
       <c r="L35" t="n">
-        <v>35.7</v>
+        <v>37.5</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3253,7 +3251,7 @@
         <v>21</v>
       </c>
       <c r="L41" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3419,7 +3417,7 @@
         <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>66.7</v>
+        <v>58.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -4883,13 +4881,18 @@
           <t>SOLO RUN</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5130,13 +5133,18 @@
           <t>SOLO RUN</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>H AIDI</t>
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12210,18 +12218,13 @@
           <t>BEFORE DESH 2 TEMP TRANSMITTER CALIBRATION (20HAH46CT001, 10HAH36CT009, 10HAH36CT009)</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D294" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E294" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -16057,13 +16060,18 @@
           <t>DEAERATOR TANK LEVEL 2 TRANSMITTER 10LAA20CL002</t>
         </is>
       </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="D443" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -17573,18 +17581,13 @@
           <t>MSW10HHC10CT101 : UNIT 1 COMBUSTOR LOWER TEMP 10HHC01CT011</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
-        </is>
-      </c>
       <c r="D500" t="inlineStr">
         <is>
           <t>M TOHER</t>
         </is>
       </c>
       <c r="E500" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -18114,18 +18117,13 @@
           <t>INSPECTION AND CALIBRATION TEMP TRANSMITTER 10LBA10CT001</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D522" t="inlineStr">
         <is>
           <t>M ZAINI</t>
         </is>
       </c>
       <c r="E522" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -23786,18 +23784,13 @@
           <t>10HAH46CT001: TEMPERATURE AFTER DESH 2</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D746" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E746" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H746" t="n">
         <v>0</v>
@@ -23814,18 +23807,13 @@
           <t>10HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
         </is>
       </c>
-      <c r="C747" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
       <c r="D747" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E747" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H747" t="n">
         <v>0</v>
@@ -23842,18 +23830,13 @@
           <t>10HAH46CT010: TEMPERATURE AFTER DESH 1</t>
         </is>
       </c>
-      <c r="C748" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="D748" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E748" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -23870,18 +23853,13 @@
           <t>10HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
-      <c r="C749" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
       <c r="D749" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E749" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -24270,7 +24248,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -29049,7 +29027,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESP </t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -31398,8 +31376,13 @@
           <t>-1750 - 0 mmH20</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="H60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -32546,9 +32529,12 @@
         </is>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -32579,15 +32565,13 @@
           <t>0-600 °C</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -32618,13 +32602,8 @@
           <t>0-600 °C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>30/08/2026</t>
-        </is>
-      </c>
       <c r="H4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -32660,15 +32639,13 @@
           <t>0-600 °C</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -32699,19 +32676,14 @@
           <t>0-1200 °C</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -32741,19 +32713,14 @@
           <t>0-1200 °C</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
       <c r="H7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -32783,19 +32750,14 @@
           <t>0-1200 °C</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -32961,19 +32923,14 @@
           <t>0-600 °C</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>22/08/2026</t>
-        </is>
-      </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -33077,15 +33034,13 @@
           <t>0-1200 °C</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>29/8/2026</t>
-        </is>
-      </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -33840,26 +33795,10 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -33868,6 +33807,7 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -35453,7 +35393,7 @@
     <row r="2" ht="24.9" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>BOILER TEST EQUIPMENT</t>
+          <t>1. BOILER TEST EQUIPMENT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1495,9 +1495,14 @@
           <t>22/08/2026</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1509,13 +1514,14 @@
         <v>12</v>
       </c>
       <c r="L10" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
@@ -6965,13 +6971,18 @@
           <t>UNIT 1 PRIMARY AIR FAN 1 OUTLET MOV</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>MSW</t>
         </is>
       </c>
       <c r="E88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -27011,17 +27022,22 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -27053,17 +27069,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -27095,17 +27116,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -29744,6 +29770,9 @@
       </c>
       <c r="L19" t="n">
         <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -33795,10 +33824,6 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>OK</t>
@@ -33807,7 +33832,6 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>0</v>
       </c>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -3768,7 +3768,7 @@
         <v>8</v>
       </c>
       <c r="L47" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -19188,13 +19188,18 @@
           <t>LIVE STEAM PRESSURE TRANSMITTER 10LBA10CP001</t>
         </is>
       </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
       <c r="D539" t="inlineStr">
         <is>
           <t>JAPA</t>
         </is>
       </c>
       <c r="E539" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -26059,7 +26064,6 @@
       <c r="K21" t="b">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -32908,6 +32912,16 @@
       </c>
       <c r="H85" t="b">
         <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Drift calibration +0.5%</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Zero &amp; span recalibrated</t>
+        </is>
       </c>
       <c r="L85" t="n">
         <v>0</v>

--- a/Template_Outage_EIC_Monitoring_unit 1.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 1.xlsx
@@ -1200,18 +1200,10 @@
           <t>SUPERVISE, QC, OTHER TASK AS PER EIC JP</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Mati</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Hidup</t>
-        </is>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="24.9" customHeight="1">
